--- a/singapore_stations.xlsx
+++ b/singapore_stations.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uogcloud-my.sharepoint.com/personal/ac3005g_gre_ac_uk/Documents/COMP1938 - Advanced Programming/Coursework/comp1938_coursework/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="11_34FF6F5B68D74AE62BE44C2F3B03ACD57F4C09EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B74B670E-3FD8-42B8-A9D6-278111FA7238}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_34FF6F5B68D74AE62BE44C2F3B03ACD57F4C09EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{331F2AA7-9D5D-44F8-BD81-19262DEAFA6A}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="1515" windowWidth="26190" windowHeight="16845" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="stations" sheetId="1" r:id="rId1"/>
     <sheet name="lines" sheetId="2" r:id="rId2"/>
     <sheet name="connections" sheetId="3" r:id="rId3"/>
+    <sheet name="station_line" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="366">
   <si>
     <t>cur_station</t>
   </si>
@@ -48,9 +49,6 @@
     <t>y</t>
   </si>
   <si>
-    <t>line_codes</t>
-  </si>
-  <si>
     <t>lon</t>
   </si>
   <si>
@@ -123,9 +121,6 @@
     <t>Promenade</t>
   </si>
   <si>
-    <t>CC DT</t>
-  </si>
-  <si>
     <t>MacPherson</t>
   </si>
   <si>
@@ -135,18 +130,12 @@
     <t>Paya Lebar</t>
   </si>
   <si>
-    <t>CC EW</t>
-  </si>
-  <si>
     <t>Buona Vista</t>
   </si>
   <si>
     <t>Bayfront</t>
   </si>
   <si>
-    <t>CE DT</t>
-  </si>
-  <si>
     <t>Changi Airport</t>
   </si>
   <si>
@@ -222,15 +211,9 @@
     <t>Expo</t>
   </si>
   <si>
-    <t>DT CG</t>
-  </si>
-  <si>
     <t>Stevens</t>
   </si>
   <si>
-    <t>DT TE</t>
-  </si>
-  <si>
     <t>Pasir Ris</t>
   </si>
   <si>
@@ -309,15 +292,9 @@
     <t>Tanah Merah</t>
   </si>
   <si>
-    <t>EW CG</t>
-  </si>
-  <si>
     <t>Tampines</t>
   </si>
   <si>
-    <t>EW DT</t>
-  </si>
-  <si>
     <t>Bugis</t>
   </si>
   <si>
@@ -354,33 +331,21 @@
     <t>Serangoon</t>
   </si>
   <si>
-    <t>NE CC</t>
-  </si>
-  <si>
     <t>HarbourFront</t>
   </si>
   <si>
     <t>Chinatown</t>
   </si>
   <si>
-    <t>NE DT</t>
-  </si>
-  <si>
     <t>Little India</t>
   </si>
   <si>
     <t>Outram Park</t>
   </si>
   <si>
-    <t>NE EW TE</t>
-  </si>
-  <si>
     <t>Punggol</t>
   </si>
   <si>
-    <t>NE PE</t>
-  </si>
-  <si>
     <t>Bukit Batok</t>
   </si>
   <si>
@@ -438,27 +403,15 @@
     <t>Choa Chu Kang</t>
   </si>
   <si>
-    <t>NS BP</t>
-  </si>
-  <si>
     <t>Bishan</t>
   </si>
   <si>
-    <t>NS CC</t>
-  </si>
-  <si>
     <t>Newton</t>
   </si>
   <si>
-    <t>NS DT</t>
-  </si>
-  <si>
     <t>Jurong East</t>
   </si>
   <si>
-    <t>NS EW</t>
-  </si>
-  <si>
     <t>City Hall</t>
   </si>
   <si>
@@ -468,15 +421,9 @@
     <t>Dhoby Ghaut</t>
   </si>
   <si>
-    <t>NS NE CC</t>
-  </si>
-  <si>
     <t>Woodlands</t>
   </si>
   <si>
-    <t>NS TE</t>
-  </si>
-  <si>
     <t>Orchard</t>
   </si>
   <si>
@@ -564,9 +511,6 @@
     <t>Caldecott</t>
   </si>
   <si>
-    <t>TE CC</t>
-  </si>
-  <si>
     <t>code</t>
   </si>
   <si>
@@ -600,10 +544,583 @@
     <t>Xilin</t>
   </si>
   <si>
-    <t>TE DT</t>
-  </si>
-  <si>
     <t>Hume</t>
+  </si>
+  <si>
+    <t>colour</t>
+  </si>
+  <si>
+    <t>#8c5d27</t>
+  </si>
+  <si>
+    <t>#c13e31</t>
+  </si>
+  <si>
+    <t>#4f924d</t>
+  </si>
+  <si>
+    <t>#3653b1</t>
+  </si>
+  <si>
+    <t>#e2a33a</t>
+  </si>
+  <si>
+    <t>#861ca4</t>
+  </si>
+  <si>
+    <t>#2c2924</t>
+  </si>
+  <si>
+    <t>station_id</t>
+  </si>
+  <si>
+    <t>line_id</t>
+  </si>
+  <si>
+    <t>dotted</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>solid</t>
+  </si>
+  <si>
+    <t>dashdot</t>
+  </si>
+  <si>
+    <t>name_direction</t>
+  </si>
+  <si>
+    <t>station_code</t>
+  </si>
+  <si>
+    <t>DT1</t>
+  </si>
+  <si>
+    <t>CC2</t>
+  </si>
+  <si>
+    <t>CC3</t>
+  </si>
+  <si>
+    <t>CC5</t>
+  </si>
+  <si>
+    <t>CC6</t>
+  </si>
+  <si>
+    <t>CC7</t>
+  </si>
+  <si>
+    <t>CC8</t>
+  </si>
+  <si>
+    <t>CC11</t>
+  </si>
+  <si>
+    <t>CC12</t>
+  </si>
+  <si>
+    <t>CC14</t>
+  </si>
+  <si>
+    <t>CC16</t>
+  </si>
+  <si>
+    <t>CC19</t>
+  </si>
+  <si>
+    <t>CC20</t>
+  </si>
+  <si>
+    <t>CC22</t>
+  </si>
+  <si>
+    <t>CC23</t>
+  </si>
+  <si>
+    <t>CC24</t>
+  </si>
+  <si>
+    <t>CC25</t>
+  </si>
+  <si>
+    <t>CC26</t>
+  </si>
+  <si>
+    <t>CC27</t>
+  </si>
+  <si>
+    <t>DT15</t>
+  </si>
+  <si>
+    <t>CC4</t>
+  </si>
+  <si>
+    <t>DT26</t>
+  </si>
+  <si>
+    <t>CC10</t>
+  </si>
+  <si>
+    <t>DT9</t>
+  </si>
+  <si>
+    <t>CC18</t>
+  </si>
+  <si>
+    <t>EW8</t>
+  </si>
+  <si>
+    <t>CC9</t>
+  </si>
+  <si>
+    <t>EW21</t>
+  </si>
+  <si>
+    <t>CC21</t>
+  </si>
+  <si>
+    <t>DT16</t>
+  </si>
+  <si>
+    <t>CC30</t>
+  </si>
+  <si>
+    <t>CG3</t>
+  </si>
+  <si>
+    <t>DT2</t>
+  </si>
+  <si>
+    <t>DT3</t>
+  </si>
+  <si>
+    <t>DT5</t>
+  </si>
+  <si>
+    <t>DT6</t>
+  </si>
+  <si>
+    <t>DT7</t>
+  </si>
+  <si>
+    <t>DT8</t>
+  </si>
+  <si>
+    <t>DT13</t>
+  </si>
+  <si>
+    <t>DT17</t>
+  </si>
+  <si>
+    <t>DT18</t>
+  </si>
+  <si>
+    <t>DT20</t>
+  </si>
+  <si>
+    <t>DT21</t>
+  </si>
+  <si>
+    <t>DT22</t>
+  </si>
+  <si>
+    <t>DT23</t>
+  </si>
+  <si>
+    <t>DT24</t>
+  </si>
+  <si>
+    <t>DT25</t>
+  </si>
+  <si>
+    <t>DT27</t>
+  </si>
+  <si>
+    <t>DT28</t>
+  </si>
+  <si>
+    <t>DT29</t>
+  </si>
+  <si>
+    <t>DT30</t>
+  </si>
+  <si>
+    <t>DT31</t>
+  </si>
+  <si>
+    <t>DT33</t>
+  </si>
+  <si>
+    <t>DT34</t>
+  </si>
+  <si>
+    <t>DT35</t>
+  </si>
+  <si>
+    <t>CG2</t>
+  </si>
+  <si>
+    <t>TE10</t>
+  </si>
+  <si>
+    <t>DT10</t>
+  </si>
+  <si>
+    <t>EW1</t>
+  </si>
+  <si>
+    <t>EW3</t>
+  </si>
+  <si>
+    <t>EW5</t>
+  </si>
+  <si>
+    <t>EW6</t>
+  </si>
+  <si>
+    <t>EW7</t>
+  </si>
+  <si>
+    <t>EW9</t>
+  </si>
+  <si>
+    <t>EW10</t>
+  </si>
+  <si>
+    <t>EW11</t>
+  </si>
+  <si>
+    <t>EW15</t>
+  </si>
+  <si>
+    <t>EW17</t>
+  </si>
+  <si>
+    <t>EW18</t>
+  </si>
+  <si>
+    <t>EW19</t>
+  </si>
+  <si>
+    <t>EW20</t>
+  </si>
+  <si>
+    <t>EW22</t>
+  </si>
+  <si>
+    <t>EW23</t>
+  </si>
+  <si>
+    <t>EW25</t>
+  </si>
+  <si>
+    <t>EW26</t>
+  </si>
+  <si>
+    <t>EW27</t>
+  </si>
+  <si>
+    <t>EW28</t>
+  </si>
+  <si>
+    <t>EW29</t>
+  </si>
+  <si>
+    <t>EW30</t>
+  </si>
+  <si>
+    <t>EW31</t>
+  </si>
+  <si>
+    <t>EW32</t>
+  </si>
+  <si>
+    <t>EW33</t>
+  </si>
+  <si>
+    <t>EW4</t>
+  </si>
+  <si>
+    <t>CG1</t>
+  </si>
+  <si>
+    <t>EW2</t>
+  </si>
+  <si>
+    <t>DT32</t>
+  </si>
+  <si>
+    <t>EW12</t>
+  </si>
+  <si>
+    <t>DT14</t>
+  </si>
+  <si>
+    <t>NE4</t>
+  </si>
+  <si>
+    <t>NE7</t>
+  </si>
+  <si>
+    <t>NE8</t>
+  </si>
+  <si>
+    <t>NE9</t>
+  </si>
+  <si>
+    <t>NE10</t>
+  </si>
+  <si>
+    <t>NE12</t>
+  </si>
+  <si>
+    <t>NE13</t>
+  </si>
+  <si>
+    <t>NE14</t>
+  </si>
+  <si>
+    <t>NE15</t>
+  </si>
+  <si>
+    <t>CC13</t>
+  </si>
+  <si>
+    <t>NE11</t>
+  </si>
+  <si>
+    <t>CC28</t>
+  </si>
+  <si>
+    <t>NE1</t>
+  </si>
+  <si>
+    <t>STE1</t>
+  </si>
+  <si>
+    <t>DT19</t>
+  </si>
+  <si>
+    <t>NE3</t>
+  </si>
+  <si>
+    <t>DT12</t>
+  </si>
+  <si>
+    <t>NE6</t>
+  </si>
+  <si>
+    <t>TE16</t>
+  </si>
+  <si>
+    <t>EW16</t>
+  </si>
+  <si>
+    <t>NE16</t>
+  </si>
+  <si>
+    <t>NS2</t>
+  </si>
+  <si>
+    <t>NS3</t>
+  </si>
+  <si>
+    <t>NS5</t>
+  </si>
+  <si>
+    <t>NS6</t>
+  </si>
+  <si>
+    <t>NS7</t>
+  </si>
+  <si>
+    <t>NS9</t>
+  </si>
+  <si>
+    <t>NS10</t>
+  </si>
+  <si>
+    <t>NS11</t>
+  </si>
+  <si>
+    <t>NS12</t>
+  </si>
+  <si>
+    <t>NS13</t>
+  </si>
+  <si>
+    <t>NS14</t>
+  </si>
+  <si>
+    <t>NS15</t>
+  </si>
+  <si>
+    <t>NS17</t>
+  </si>
+  <si>
+    <t>NS18</t>
+  </si>
+  <si>
+    <t>NS19</t>
+  </si>
+  <si>
+    <t>NS22</t>
+  </si>
+  <si>
+    <t>NS27</t>
+  </si>
+  <si>
+    <t>NS4</t>
+  </si>
+  <si>
+    <t>NS16</t>
+  </si>
+  <si>
+    <t>CC15</t>
+  </si>
+  <si>
+    <t>NS20</t>
+  </si>
+  <si>
+    <t>DT11</t>
+  </si>
+  <si>
+    <t>NS1</t>
+  </si>
+  <si>
+    <t>EW24</t>
+  </si>
+  <si>
+    <t>NS24</t>
+  </si>
+  <si>
+    <t>EW13</t>
+  </si>
+  <si>
+    <t>NS25</t>
+  </si>
+  <si>
+    <t>EW14</t>
+  </si>
+  <si>
+    <t>NS23</t>
+  </si>
+  <si>
+    <t>CC1</t>
+  </si>
+  <si>
+    <t>NE5</t>
+  </si>
+  <si>
+    <t>TE2</t>
+  </si>
+  <si>
+    <t>NS8</t>
+  </si>
+  <si>
+    <t>TE13</t>
+  </si>
+  <si>
+    <t>NS21</t>
+  </si>
+  <si>
+    <t>TE19</t>
+  </si>
+  <si>
+    <t>NS26</t>
+  </si>
+  <si>
+    <t>STE2</t>
+  </si>
+  <si>
+    <t>TE1</t>
+  </si>
+  <si>
+    <t>TE3</t>
+  </si>
+  <si>
+    <t>TE4</t>
+  </si>
+  <si>
+    <t>TE5</t>
+  </si>
+  <si>
+    <t>TE6</t>
+  </si>
+  <si>
+    <t>TE7</t>
+  </si>
+  <si>
+    <t>TE8</t>
+  </si>
+  <si>
+    <t>TE11</t>
+  </si>
+  <si>
+    <t>TE12</t>
+  </si>
+  <si>
+    <t>TE14</t>
+  </si>
+  <si>
+    <t>TE15</t>
+  </si>
+  <si>
+    <t>TE17</t>
+  </si>
+  <si>
+    <t>TE18</t>
+  </si>
+  <si>
+    <t>TE20</t>
+  </si>
+  <si>
+    <t>TE21</t>
+  </si>
+  <si>
+    <t>TE22</t>
+  </si>
+  <si>
+    <t>TE23</t>
+  </si>
+  <si>
+    <t>TE24</t>
+  </si>
+  <si>
+    <t>TE25</t>
+  </si>
+  <si>
+    <t>TE26</t>
+  </si>
+  <si>
+    <t>TE27</t>
+  </si>
+  <si>
+    <t>TE28</t>
+  </si>
+  <si>
+    <t>TE29</t>
+  </si>
+  <si>
+    <t>DT37</t>
+  </si>
+  <si>
+    <t>TE9</t>
+  </si>
+  <si>
+    <t>CC17</t>
+  </si>
+  <si>
+    <t>DT36</t>
+  </si>
+  <si>
+    <t>DT4</t>
+  </si>
+  <si>
+    <t>NE17</t>
   </si>
 </sst>
 </file>
@@ -627,7 +1144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -637,6 +1154,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -663,6 +1186,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,6 +1217,16 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{24401E3E-959A-4BB2-B642-FF3781CED31B}" name="station_line_tbl" displayName="station_line_tbl" ref="A1:B177" totalsRowShown="0">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{0127A775-7225-43DE-B179-2A76E766AFC8}" name="station_id"/>
+    <tableColumn id="2" xr3:uid="{EECA1B8F-D0B2-406D-9B2C-9F956213311C}" name="line_id"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1017,8 +1551,8 @@
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1041,7 +1575,7 @@
         <v>9</v>
       </c>
       <c r="G1" t="s">
-        <v>10</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1049,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>0.24946300093996401</v>
@@ -1057,13 +1591,10 @@
       <c r="D2">
         <v>0.31241533336156602</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
+      <c r="E2">
+        <v>103.75959784357281</v>
       </c>
       <c r="F2">
-        <v>103.75959784357281</v>
-      </c>
-      <c r="G2">
         <v>1.380745117305777</v>
       </c>
     </row>
@@ -1072,7 +1603,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0.61586143909351998</v>
@@ -1080,13 +1611,10 @@
       <c r="D3">
         <v>0.72270082341692599</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
+      <c r="E3">
+        <v>103.85047427550749</v>
       </c>
       <c r="F3">
-        <v>103.85047427550749</v>
-      </c>
-      <c r="G3">
         <v>1.296046213077239</v>
       </c>
     </row>
@@ -1095,7 +1623,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>0.67111874415148098</v>
@@ -1103,13 +1631,10 @@
       <c r="D4">
         <v>0.78295253873974102</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
+      <c r="E4">
+        <v>103.8555678410694</v>
       </c>
       <c r="F4">
-        <v>103.8555678410694</v>
-      </c>
-      <c r="G4">
         <v>1.2931288136602319</v>
       </c>
     </row>
@@ -1118,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>0.77058189325581095</v>
@@ -1126,13 +1651,10 @@
       <c r="D5">
         <v>0.76191225719844002</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
+      <c r="E5">
+        <v>103.8635059552432</v>
       </c>
       <c r="F5">
-        <v>103.8635059552432</v>
-      </c>
-      <c r="G5">
         <v>1.3001696897088439</v>
       </c>
     </row>
@@ -1141,7 +1663,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>0.78588391619493903</v>
@@ -1149,13 +1671,10 @@
       <c r="D6">
         <v>0.71983169411583903</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
+      <c r="E6">
+        <v>103.8762262339748</v>
       </c>
       <c r="F6">
-        <v>103.8762262339748</v>
-      </c>
-      <c r="G6">
         <v>1.303370226020246</v>
       </c>
     </row>
@@ -1164,7 +1683,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>0.79438504005000998</v>
@@ -1172,13 +1691,10 @@
       <c r="D7">
         <v>0.67583837816584702</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
+      <c r="E7">
+        <v>103.8832482927035</v>
       </c>
       <c r="F7">
-        <v>103.8832482927035</v>
-      </c>
-      <c r="G7">
         <v>1.3060459256607551</v>
       </c>
     </row>
@@ -1187,7 +1703,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>0.79608526482102404</v>
@@ -1195,13 +1711,10 @@
       <c r="D8">
         <v>0.63471419151694197</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
+      <c r="E8">
+        <v>103.8893072153439</v>
       </c>
       <c r="F8">
-        <v>103.8893072153439</v>
-      </c>
-      <c r="G8">
         <v>1.3088141875242589</v>
       </c>
     </row>
@@ -1210,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>0.74677874646161302</v>
@@ -1218,13 +1731,10 @@
       <c r="D9">
         <v>0.47117382135501501</v>
       </c>
-      <c r="E9" t="s">
-        <v>14</v>
+      <c r="E9">
+        <v>103.8882140677722</v>
       </c>
       <c r="F9">
-        <v>103.8882140677722</v>
-      </c>
-      <c r="G9">
         <v>1.3346208772307531</v>
       </c>
     </row>
@@ -1233,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>0.71362436342683599</v>
@@ -1241,13 +1751,10 @@
       <c r="D10">
         <v>0.43387514044089098</v>
       </c>
-      <c r="E10" t="s">
-        <v>14</v>
+      <c r="E10">
+        <v>103.8789086939245</v>
       </c>
       <c r="F10">
-        <v>103.8789086939245</v>
-      </c>
-      <c r="G10">
         <v>1.3435010615293339</v>
       </c>
     </row>
@@ -1256,7 +1763,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>0.60395986569642102</v>
@@ -1264,13 +1771,10 @@
       <c r="D11">
         <v>0.36692879008220802</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
+      <c r="E11">
+        <v>103.86291829995641</v>
       </c>
       <c r="F11">
-        <v>103.86291829995641</v>
-      </c>
-      <c r="G11">
         <v>1.351738537912768</v>
       </c>
     </row>
@@ -1279,7 +1783,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>0.468791996400793</v>
@@ -1287,13 +1791,10 @@
       <c r="D12">
         <v>0.37553617798546701</v>
       </c>
-      <c r="E12" t="s">
-        <v>14</v>
+      <c r="E12">
+        <v>103.8400589180772</v>
       </c>
       <c r="F12">
-        <v>103.8400589180772</v>
-      </c>
-      <c r="G12">
         <v>1.347866072173078</v>
       </c>
     </row>
@@ -1302,7 +1803,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>0.32172255370806702</v>
@@ -1310,13 +1811,10 @@
       <c r="D13">
         <v>0.53142553667782999</v>
       </c>
-      <c r="E13" t="s">
-        <v>14</v>
+      <c r="E13">
+        <v>103.80796523070789</v>
       </c>
       <c r="F13">
-        <v>103.80796523070789</v>
-      </c>
-      <c r="G13">
         <v>1.3174937258955099</v>
       </c>
     </row>
@@ -1325,7 +1823,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14">
         <v>0.308120755539953</v>
@@ -1333,13 +1831,10 @@
       <c r="D14">
         <v>0.57924435836260402</v>
       </c>
-      <c r="E14" t="s">
-        <v>14</v>
+      <c r="E14">
+        <v>103.79575377011339</v>
       </c>
       <c r="F14">
-        <v>103.79575377011339</v>
-      </c>
-      <c r="G14">
         <v>1.310711201332724</v>
       </c>
     </row>
@@ -1348,7 +1843,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15">
         <v>0.30302008122690999</v>
@@ -1356,13 +1851,10 @@
       <c r="D15">
         <v>0.67775113103323803</v>
       </c>
-      <c r="E15" t="s">
-        <v>14</v>
+      <c r="E15">
+        <v>103.7877848105538</v>
       </c>
       <c r="F15">
-        <v>103.7877848105538</v>
-      </c>
-      <c r="G15">
         <v>1.300074702884209</v>
       </c>
     </row>
@@ -1371,7 +1863,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0.313221429852996</v>
@@ -1379,22 +1871,19 @@
       <c r="D16">
         <v>0.72174444698323004</v>
       </c>
-      <c r="E16" t="s">
-        <v>14</v>
+      <c r="E16">
+        <v>103.784490451682</v>
       </c>
       <c r="F16">
-        <v>103.784490451682</v>
-      </c>
-      <c r="G16">
         <v>1.2939847851670141</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>0.32682322802110902</v>
@@ -1402,22 +1891,19 @@
       <c r="D17">
         <v>0.76286863363213597</v>
       </c>
-      <c r="E17" t="s">
-        <v>14</v>
+      <c r="E17">
+        <v>103.78200639707239</v>
       </c>
       <c r="F17">
-        <v>103.78200639707239</v>
-      </c>
-      <c r="G17">
         <v>1.2830552735417651</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>0.34297536334574402</v>
@@ -1425,22 +1911,19 @@
       <c r="D18">
         <v>0.79347267951039102</v>
       </c>
-      <c r="E18" t="s">
-        <v>14</v>
+      <c r="E18">
+        <v>103.7920301869204</v>
       </c>
       <c r="F18">
-        <v>103.7920301869204</v>
-      </c>
-      <c r="G18">
         <v>1.2760032327850539</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>0.366778510139942</v>
@@ -1448,22 +1931,19 @@
       <c r="D19">
         <v>0.82885860755712404</v>
       </c>
-      <c r="E19" t="s">
-        <v>14</v>
+      <c r="E19">
+        <v>103.80235555366291</v>
       </c>
       <c r="F19">
-        <v>103.80235555366291</v>
-      </c>
-      <c r="G19">
         <v>1.2721069580543349</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20">
         <v>0.39823266840370503</v>
@@ -1471,45 +1951,39 @@
       <c r="D20">
         <v>0.85946265343537898</v>
       </c>
-      <c r="E20" t="s">
-        <v>14</v>
+      <c r="E20">
+        <v>103.80988373092021</v>
       </c>
       <c r="F20">
-        <v>103.80988373092021</v>
-      </c>
-      <c r="G20">
         <v>1.270721226211404</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5">
         <v>0.74252818453407698</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="5">
         <v>0.80494919671473697</v>
       </c>
-      <c r="E21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21">
+      <c r="E21" s="5">
         <v>103.86013688440229</v>
       </c>
-      <c r="G21">
+      <c r="F21" s="5">
         <v>1.293862087876265</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>0.772282118026825</v>
@@ -1517,22 +1991,19 @@
       <c r="D22">
         <v>0.51899264303978898</v>
       </c>
-      <c r="E22" t="s">
-        <v>33</v>
+      <c r="E22">
+        <v>103.8886152116773</v>
       </c>
       <c r="F22">
-        <v>103.8886152116773</v>
-      </c>
-      <c r="G22">
         <v>1.326192777550482</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23">
         <v>0.34977626242980098</v>
@@ -1540,22 +2011,19 @@
       <c r="D23">
         <v>0.47595570352349198</v>
       </c>
-      <c r="E23" t="s">
-        <v>33</v>
+      <c r="E23">
+        <v>103.8159141457915</v>
       </c>
       <c r="F23">
-        <v>103.8159141457915</v>
-      </c>
-      <c r="G23">
         <v>1.32268461233639</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C24">
         <v>0.79183470289348801</v>
@@ -1563,22 +2031,19 @@
       <c r="D24">
         <v>0.58211348766369098</v>
       </c>
-      <c r="E24" t="s">
-        <v>37</v>
+      <c r="E24">
+        <v>103.8927883241053</v>
       </c>
       <c r="F24">
-        <v>103.8927883241053</v>
-      </c>
-      <c r="G24">
         <v>1.318215992150078</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C25">
         <v>0.30216996884140301</v>
@@ -1586,45 +2051,39 @@
       <c r="D25">
         <v>0.63758332081802804</v>
       </c>
-      <c r="E25" t="s">
-        <v>37</v>
+      <c r="E25">
+        <v>103.7904491753026</v>
       </c>
       <c r="F25">
-        <v>103.7904491753026</v>
-      </c>
-      <c r="G25">
         <v>1.307309450770241</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="5">
         <v>0.70172279002973703</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="5">
         <v>0.85754990056798797</v>
       </c>
-      <c r="E26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26">
+      <c r="E26" s="5">
         <v>103.8595968721875</v>
       </c>
-      <c r="G26">
+      <c r="F26" s="5">
         <v>1.2828349086889399</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C27">
         <v>1.1055261731456001</v>
@@ -1632,22 +2091,19 @@
       <c r="D27">
         <v>0.51038525513652999</v>
       </c>
-      <c r="E27" t="s">
-        <v>42</v>
+      <c r="E27">
+        <v>103.9892766424138</v>
       </c>
       <c r="F27">
-        <v>103.9892766424138</v>
-      </c>
-      <c r="G27">
         <v>1.356341421004803</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>0.24946300093996401</v>
@@ -1655,22 +2111,19 @@
       <c r="D28">
         <v>0.33441199133656102</v>
       </c>
-      <c r="E28" t="s">
-        <v>12</v>
+      <c r="E28">
+        <v>103.764234480711</v>
       </c>
       <c r="F28">
-        <v>103.764234480711</v>
-      </c>
-      <c r="G28">
         <v>1.369833318596293</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C29">
         <v>0.24861288855445701</v>
@@ -1678,22 +2131,19 @@
       <c r="D29">
         <v>0.35640864931155802</v>
       </c>
-      <c r="E29" t="s">
-        <v>12</v>
+      <c r="E29">
+        <v>103.7676882901031</v>
       </c>
       <c r="F29">
-        <v>103.7676882901031</v>
-      </c>
-      <c r="G29">
         <v>1.3624742379450681</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>0.24946300093996401</v>
@@ -1701,22 +2151,19 @@
       <c r="D30">
         <v>0.40231471812894098</v>
       </c>
-      <c r="E30" t="s">
-        <v>12</v>
+      <c r="E30">
+        <v>103.7759842962261</v>
       </c>
       <c r="F30">
-        <v>103.7759842962261</v>
-      </c>
-      <c r="G30">
         <v>1.3416961499328011</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>0.25031311332547102</v>
@@ -1724,22 +2171,19 @@
       <c r="D31">
         <v>0.42335499967024098</v>
       </c>
-      <c r="E31" t="s">
-        <v>12</v>
+      <c r="E31">
+        <v>103.7845615847806</v>
       </c>
       <c r="F31">
-        <v>103.7845615847806</v>
-      </c>
-      <c r="G31">
         <v>1.33597604551556</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>0.24946300093996401</v>
@@ -1747,22 +2191,19 @@
       <c r="D32">
         <v>0.44439528121154198</v>
       </c>
-      <c r="E32" t="s">
-        <v>12</v>
+      <c r="E32">
+        <v>103.7968481782287</v>
       </c>
       <c r="F32">
-        <v>103.7968481782287</v>
-      </c>
-      <c r="G32">
         <v>1.331521301435717</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C33">
         <v>0.28856817067328999</v>
@@ -1770,22 +2211,19 @@
       <c r="D33">
         <v>0.47691207995718798</v>
       </c>
-      <c r="E33" t="s">
-        <v>12</v>
+      <c r="E33">
+        <v>103.8078008737065</v>
       </c>
       <c r="F33">
-        <v>103.8078008737065</v>
-      </c>
-      <c r="G33">
         <v>1.326146158825493</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C34">
         <v>0.60821042762395605</v>
@@ -1793,22 +2231,19 @@
       <c r="D34">
         <v>0.63567056795063703</v>
       </c>
-      <c r="E34" t="s">
-        <v>12</v>
+      <c r="E34">
+        <v>103.85310433564941</v>
       </c>
       <c r="F34">
-        <v>103.85310433564941</v>
-      </c>
-      <c r="G34">
         <v>1.3042147770337429</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <v>0.645615372586269</v>
@@ -1816,22 +2251,19 @@
       <c r="D35">
         <v>0.87093917063972504</v>
       </c>
-      <c r="E35" t="s">
-        <v>12</v>
+      <c r="E35">
+        <v>103.8526465600109</v>
       </c>
       <c r="F35">
-        <v>103.8526465600109</v>
-      </c>
-      <c r="G35">
         <v>1.2797734552829649</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C36">
         <v>0.574205932203673</v>
@@ -1839,22 +2271,19 @@
       <c r="D36">
         <v>0.82312034895495101</v>
       </c>
-      <c r="E36" t="s">
-        <v>12</v>
+      <c r="E36">
+        <v>103.8488416560614</v>
       </c>
       <c r="F36">
-        <v>103.8488416560614</v>
-      </c>
-      <c r="G36">
         <v>1.2822506642640741</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C37">
         <v>0.49684570512252701</v>
@@ -1862,22 +2291,19 @@
       <c r="D37">
         <v>0.69974778900823398</v>
       </c>
-      <c r="E37" t="s">
-        <v>12</v>
+      <c r="E37">
+        <v>103.84442503156529</v>
       </c>
       <c r="F37">
-        <v>103.84442503156529</v>
-      </c>
-      <c r="G37">
         <v>1.292830275945718</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C38">
         <v>0.62776301249062005</v>
@@ -1885,22 +2311,19 @@
       <c r="D38">
         <v>0.68731489537019297</v>
       </c>
-      <c r="E38" t="s">
-        <v>12</v>
+      <c r="E38">
+        <v>103.8492717038725</v>
       </c>
       <c r="F38">
-        <v>103.8492717038725</v>
-      </c>
-      <c r="G38">
         <v>1.297699117654433</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C39">
         <v>0.65666683359786104</v>
@@ -1908,22 +2331,19 @@
       <c r="D39">
         <v>0.65288534375715601</v>
       </c>
-      <c r="E39" t="s">
-        <v>12</v>
+      <c r="E39">
+        <v>103.8552961254143</v>
       </c>
       <c r="F39">
-        <v>103.8552961254143</v>
-      </c>
-      <c r="G39">
         <v>1.304889894129293</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C40">
         <v>0.69407177856017299</v>
@@ -1931,22 +2351,19 @@
       <c r="D40">
         <v>0.61176115710824996</v>
       </c>
-      <c r="E40" t="s">
-        <v>12</v>
+      <c r="E40">
+        <v>103.86307400593709</v>
       </c>
       <c r="F40">
-        <v>103.86307400593709</v>
-      </c>
-      <c r="G40">
         <v>1.3138525056222501</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C41">
         <v>0.72042526251089301</v>
@@ -1954,22 +2371,19 @@
       <c r="D41">
         <v>0.58211348766369098</v>
       </c>
-      <c r="E41" t="s">
-        <v>12</v>
+      <c r="E41">
+        <v>103.87155560756931</v>
       </c>
       <c r="F41">
-        <v>103.87155560756931</v>
-      </c>
-      <c r="G41">
         <v>1.321561698740251</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C42">
         <v>0.74762885884712005</v>
@@ -1977,22 +2391,19 @@
       <c r="D42">
         <v>0.54959668891804403</v>
       </c>
-      <c r="E42" t="s">
-        <v>12</v>
+      <c r="E42">
+        <v>103.88374838731281</v>
       </c>
       <c r="F42">
-        <v>103.88374838731281</v>
-      </c>
-      <c r="G42">
         <v>1.326463522167072</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C43">
         <v>0.80713672583261598</v>
@@ -2000,22 +2411,19 @@
       <c r="D43">
         <v>0.48456309142675202</v>
       </c>
-      <c r="E43" t="s">
-        <v>12</v>
+      <c r="E43">
+        <v>103.8985855709163</v>
       </c>
       <c r="F43">
-        <v>103.8985855709163</v>
-      </c>
-      <c r="G43">
         <v>1.329830770674731</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C44">
         <v>0.83604054693985697</v>
@@ -2023,22 +2431,19 @@
       <c r="D44">
         <v>0.45013353981371401</v>
       </c>
-      <c r="E44" t="s">
-        <v>12</v>
+      <c r="E44">
+        <v>103.9091462762628</v>
       </c>
       <c r="F44">
-        <v>103.9091462762628</v>
-      </c>
-      <c r="G44">
         <v>1.334921890342718</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C45">
         <v>0.86239403089057698</v>
@@ -2046,22 +2451,19 @@
       <c r="D45">
         <v>0.42144224680284997</v>
       </c>
-      <c r="E45" t="s">
-        <v>12</v>
+      <c r="E45">
+        <v>103.9178105260292</v>
       </c>
       <c r="F45">
-        <v>103.9178105260292</v>
-      </c>
-      <c r="G45">
         <v>1.334422576551513</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C46">
         <v>0.91255066163549603</v>
@@ -2069,22 +2471,19 @@
       <c r="D46">
         <v>0.40996572959850403</v>
       </c>
-      <c r="E46" t="s">
-        <v>12</v>
+      <c r="E46">
+        <v>103.9334871898551</v>
       </c>
       <c r="F46">
-        <v>103.9334871898551</v>
-      </c>
-      <c r="G46">
         <v>1.336554903328631</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C47">
         <v>0.96185717999490705</v>
@@ -2092,22 +2491,19 @@
       <c r="D47">
         <v>0.40996572959850403</v>
       </c>
-      <c r="E47" t="s">
-        <v>12</v>
+      <c r="E47">
+        <v>103.9389485037816</v>
       </c>
       <c r="F47">
-        <v>103.9389485037816</v>
-      </c>
-      <c r="G47">
         <v>1.344999197514483</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C48">
         <v>1.0604702167137301</v>
@@ -2115,22 +2511,19 @@
       <c r="D48">
         <v>0.437700646175673</v>
       </c>
-      <c r="E48" t="s">
-        <v>12</v>
+      <c r="E48">
+        <v>103.9426536818783</v>
       </c>
       <c r="F48">
-        <v>103.9426536818783</v>
-      </c>
-      <c r="G48">
         <v>1.3541939276064221</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C49">
         <v>1.0604702167137301</v>
@@ -2138,22 +2531,19 @@
       <c r="D49">
         <v>0.46639193918653798</v>
       </c>
-      <c r="E49" t="s">
-        <v>12</v>
+      <c r="E49">
+        <v>103.9610430807089</v>
       </c>
       <c r="F49">
-        <v>103.9610430807089</v>
-      </c>
-      <c r="G49">
         <v>1.3408404740643269</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C50">
         <v>1.0604702167137301</v>
@@ -2161,22 +2551,19 @@
       <c r="D50">
         <v>0.51134163157022505</v>
       </c>
-      <c r="E50" t="s">
-        <v>66</v>
+      <c r="E50">
+        <v>103.9621610218642</v>
       </c>
       <c r="F50">
-        <v>103.9621610218642</v>
-      </c>
-      <c r="G50">
         <v>1.335950971715691</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>0.42543626473993201</v>
@@ -2184,22 +2571,19 @@
       <c r="D51">
         <v>0.47499932708979697</v>
       </c>
-      <c r="E51" t="s">
-        <v>68</v>
+      <c r="E51">
+        <v>103.82632257714459</v>
       </c>
       <c r="F51">
-        <v>103.82632257714459</v>
-      </c>
-      <c r="G51">
         <v>1.3209377434144121</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C52">
         <v>1.00521291165576</v>
@@ -2207,22 +2591,19 @@
       <c r="D52">
         <v>0.36119053148003499</v>
       </c>
-      <c r="E52" t="s">
-        <v>70</v>
+      <c r="E52">
+        <v>103.94913694034911</v>
       </c>
       <c r="F52">
-        <v>103.94913694034911</v>
-      </c>
-      <c r="G52">
         <v>1.372886236352008</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C53">
         <v>1.0035126868847499</v>
@@ -2230,22 +2611,19 @@
       <c r="D53">
         <v>0.43865702260936901</v>
       </c>
-      <c r="E53" t="s">
-        <v>70</v>
+      <c r="E53">
+        <v>103.953818676297</v>
       </c>
       <c r="F53">
-        <v>103.953818676297</v>
-      </c>
-      <c r="G53">
         <v>1.342661794533708</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C54">
         <v>0.92105178549056699</v>
@@ -2253,22 +2631,19 @@
       <c r="D54">
         <v>0.46256643345175602</v>
       </c>
-      <c r="E54" t="s">
-        <v>70</v>
+      <c r="E54">
+        <v>103.9294042796889</v>
       </c>
       <c r="F54">
-        <v>103.9294042796889</v>
-      </c>
-      <c r="G54">
         <v>1.32407464586546</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C55">
         <v>0.86324414327608401</v>
@@ -2276,22 +2651,19 @@
       <c r="D55">
         <v>0.49699598506479298</v>
       </c>
-      <c r="E55" t="s">
-        <v>70</v>
+      <c r="E55">
+        <v>103.9128992887463</v>
       </c>
       <c r="F55">
-        <v>103.9128992887463</v>
-      </c>
-      <c r="G55">
         <v>1.321152108055446</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C56">
         <v>0.82838953547029304</v>
@@ -2299,22 +2671,19 @@
       <c r="D56">
         <v>0.53620741884630796</v>
       </c>
-      <c r="E56" t="s">
-        <v>70</v>
+      <c r="E56">
+        <v>103.9032151869783</v>
       </c>
       <c r="F56">
-        <v>103.9032151869783</v>
-      </c>
-      <c r="G56">
         <v>1.3195299188012679</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C57">
         <v>0.75783020747320495</v>
@@ -2322,22 +2691,19 @@
       <c r="D57">
         <v>0.61845579214411905</v>
       </c>
-      <c r="E57" t="s">
-        <v>70</v>
+      <c r="E57">
+        <v>103.8824728877824</v>
       </c>
       <c r="F57">
-        <v>103.8824728877824</v>
-      </c>
-      <c r="G57">
         <v>1.316487930304078</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C58">
         <v>0.73147672352248505</v>
@@ -2345,22 +2711,19 @@
       <c r="D58">
         <v>0.64714708515498298</v>
       </c>
-      <c r="E58" t="s">
-        <v>70</v>
+      <c r="E58">
+        <v>103.8715870758614</v>
       </c>
       <c r="F58">
-        <v>103.8715870758614</v>
-      </c>
-      <c r="G58">
         <v>1.311781770543804</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C59">
         <v>0.70427312718625801</v>
@@ -2368,22 +2731,19 @@
       <c r="D59">
         <v>0.67870750746693398</v>
       </c>
-      <c r="E59" t="s">
-        <v>70</v>
+      <c r="E59">
+        <v>103.8630430629033</v>
       </c>
       <c r="F59">
-        <v>103.8630430629033</v>
-      </c>
-      <c r="G59">
         <v>1.307169460472736</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C60">
         <v>0.50109626705006305</v>
@@ -2391,22 +2751,19 @@
       <c r="D60">
         <v>0.84511700692994696</v>
       </c>
-      <c r="E60" t="s">
-        <v>70</v>
+      <c r="E60">
+        <v>103.8469275802349</v>
       </c>
       <c r="F60">
-        <v>103.8469275802349</v>
-      </c>
-      <c r="G60">
         <v>1.2773794881071401</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C61">
         <v>0.415234916113847</v>
@@ -2414,22 +2771,19 @@
       <c r="D61">
         <v>0.75139211642779002</v>
       </c>
-      <c r="E61" t="s">
-        <v>70</v>
+      <c r="E61">
+        <v>103.8269905951461</v>
       </c>
       <c r="F61">
-        <v>103.8269905951461</v>
-      </c>
-      <c r="G61">
         <v>1.2857594558988179</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C62">
         <v>0.38888143216312698</v>
@@ -2437,22 +2791,19 @@
       <c r="D62">
         <v>0.72078807054953498</v>
       </c>
-      <c r="E62" t="s">
-        <v>70</v>
+      <c r="E62">
+        <v>103.8169944585527</v>
       </c>
       <c r="F62">
-        <v>103.8169944585527</v>
-      </c>
-      <c r="G62">
         <v>1.289370704673515</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C63">
         <v>0.36252794821240703</v>
@@ -2460,22 +2811,19 @@
       <c r="D63">
         <v>0.69114040110497499</v>
       </c>
-      <c r="E63" t="s">
-        <v>70</v>
+      <c r="E63">
+        <v>103.805584729896</v>
       </c>
       <c r="F63">
-        <v>103.805584729896</v>
-      </c>
-      <c r="G63">
         <v>1.295446256070099</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C64">
         <v>0.33787468903270101</v>
@@ -2483,22 +2831,19 @@
       <c r="D64">
         <v>0.66627461382889297</v>
       </c>
-      <c r="E64" t="s">
-        <v>70</v>
+      <c r="E64">
+        <v>103.7987785726048</v>
       </c>
       <c r="F64">
-        <v>103.7987785726048</v>
-      </c>
-      <c r="G64">
         <v>1.3020770458031889</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C65">
         <v>0.257964124795035</v>
@@ -2506,22 +2851,19 @@
       <c r="D65">
         <v>0.63853969725172399</v>
       </c>
-      <c r="E65" t="s">
-        <v>70</v>
+      <c r="E65">
+        <v>103.7783047152878</v>
       </c>
       <c r="F65">
-        <v>103.7783047152878</v>
-      </c>
-      <c r="G65">
         <v>1.31141543344877</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C66">
         <v>0.219709067447215</v>
@@ -2529,22 +2871,19 @@
       <c r="D66">
         <v>0.63949607368541905</v>
       </c>
-      <c r="E66" t="s">
-        <v>70</v>
+      <c r="E66">
+        <v>103.7655701161836</v>
       </c>
       <c r="F66">
-        <v>103.7655701161836</v>
-      </c>
-      <c r="G66">
         <v>1.3140784143450011</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C67">
         <v>0.116845468800857</v>
@@ -2552,22 +2891,19 @@
       <c r="D67">
         <v>0.63853969725172399</v>
       </c>
-      <c r="E67" t="s">
-        <v>70</v>
+      <c r="E67">
+        <v>103.733393135763</v>
       </c>
       <c r="F67">
-        <v>103.733393135763</v>
-      </c>
-      <c r="G67">
         <v>1.341565826332578</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C68">
         <v>7.4339849525503099E-2</v>
@@ -2575,22 +2911,19 @@
       <c r="D68">
         <v>0.63853969725172399</v>
       </c>
-      <c r="E68" t="s">
-        <v>70</v>
+      <c r="E68">
+        <v>103.720448529393</v>
       </c>
       <c r="F68">
-        <v>103.720448529393</v>
-      </c>
-      <c r="G68">
         <v>1.3439833412621971</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C69">
         <v>3.43845674066698E-2</v>
@@ -2598,22 +2931,19 @@
       <c r="D69">
         <v>0.59167725200064503</v>
       </c>
-      <c r="E69" t="s">
-        <v>70</v>
+      <c r="E69">
+        <v>103.7061455479667</v>
       </c>
       <c r="F69">
-        <v>103.7061455479667</v>
-      </c>
-      <c r="G69">
         <v>1.338420695657893</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C70">
         <v>3.43845674066698E-2</v>
@@ -2621,22 +2951,19 @@
       <c r="D70">
         <v>0.55342219465282605</v>
       </c>
-      <c r="E70" t="s">
-        <v>70</v>
+      <c r="E70">
+        <v>103.69715537341131</v>
       </c>
       <c r="F70">
-        <v>103.69715537341131</v>
-      </c>
-      <c r="G70">
         <v>1.3373446269204401</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C71">
         <v>3.43845674066698E-2</v>
@@ -2644,22 +2971,19 @@
       <c r="D71">
         <v>0.51707989017239797</v>
       </c>
-      <c r="E71" t="s">
-        <v>70</v>
+      <c r="E71">
+        <v>103.67852070901129</v>
       </c>
       <c r="F71">
-        <v>103.67852070901129</v>
-      </c>
-      <c r="G71">
         <v>1.327502084458654</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C72">
         <v>3.5234679792176898E-2</v>
@@ -2667,22 +2991,19 @@
       <c r="D72">
         <v>0.47595570352349198</v>
       </c>
-      <c r="E72" t="s">
-        <v>70</v>
+      <c r="E72">
+        <v>103.66044414385929</v>
       </c>
       <c r="F72">
-        <v>103.66044414385929</v>
-      </c>
-      <c r="G72">
         <v>1.3190322665685099</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C73">
         <v>3.43845674066698E-2</v>
@@ -2690,22 +3011,19 @@
       <c r="D73">
         <v>0.43865702260936901</v>
       </c>
-      <c r="E73" t="s">
-        <v>70</v>
+      <c r="E73">
+        <v>103.64895874126709</v>
       </c>
       <c r="F73">
-        <v>103.64895874126709</v>
-      </c>
-      <c r="G73">
         <v>1.320763817112224</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C74">
         <v>3.43845674066698E-2</v>
@@ -2713,22 +3031,19 @@
       <c r="D74">
         <v>0.40231471812894098</v>
       </c>
-      <c r="E74" t="s">
-        <v>70</v>
+      <c r="E74">
+        <v>103.6392843447087</v>
       </c>
       <c r="F74">
-        <v>103.6392843447087</v>
-      </c>
-      <c r="G74">
         <v>1.3298724241392641</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C75">
         <v>3.43845674066698E-2</v>
@@ -2736,22 +3051,19 @@
       <c r="D75">
         <v>0.363103284347426</v>
       </c>
-      <c r="E75" t="s">
-        <v>70</v>
+      <c r="E75">
+        <v>103.6372457200215</v>
       </c>
       <c r="F75">
-        <v>103.6372457200215</v>
-      </c>
-      <c r="G75">
         <v>1.340426899205142</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C76">
         <v>0.98906077633113398</v>
@@ -2759,22 +3071,19 @@
       <c r="D76">
         <v>0.46161005701806002</v>
       </c>
-      <c r="E76" t="s">
-        <v>95</v>
+      <c r="E76">
+        <v>103.9457230415822</v>
       </c>
       <c r="F76">
-        <v>103.9457230415822</v>
-      </c>
-      <c r="G76">
         <v>1.3270612758143561</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C77">
         <v>1.00521291165576</v>
@@ -2782,22 +3091,19 @@
       <c r="D77">
         <v>0.393707330225681</v>
       </c>
-      <c r="E77" t="s">
-        <v>97</v>
+      <c r="E77">
+        <v>103.9426536818783</v>
       </c>
       <c r="F77">
-        <v>103.9426536818783</v>
-      </c>
-      <c r="G77">
         <v>1.3541939276064221</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C78">
         <v>0.67366908130800296</v>
@@ -2805,22 +3111,19 @@
       <c r="D78">
         <v>0.71122430621258004</v>
       </c>
-      <c r="E78" t="s">
-        <v>97</v>
+      <c r="E78">
+        <v>103.8568906548671</v>
       </c>
       <c r="F78">
-        <v>103.8568906548671</v>
-      </c>
-      <c r="G78">
         <v>1.29907884888673</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C79">
         <v>0.51809851476020496</v>
@@ -2828,22 +3131,19 @@
       <c r="D79">
         <v>0.72270082341692599</v>
       </c>
-      <c r="E79" t="s">
-        <v>100</v>
+      <c r="E79">
+        <v>103.846665833855</v>
       </c>
       <c r="F79">
-        <v>103.846665833855</v>
-      </c>
-      <c r="G79">
         <v>1.289383851872467</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C80">
         <v>0.57080548266164399</v>
@@ -2851,22 +3151,19 @@
       <c r="D80">
         <v>0.554378571086522</v>
       </c>
-      <c r="E80" t="s">
-        <v>100</v>
+      <c r="E80">
+        <v>103.8547637677557</v>
       </c>
       <c r="F80">
-        <v>103.8547637677557</v>
-      </c>
-      <c r="G80">
         <v>1.3135439659756989</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C81">
         <v>0.56995537027613696</v>
@@ -2874,22 +3171,19 @@
       <c r="D81">
         <v>0.51325438443761595</v>
       </c>
-      <c r="E81" t="s">
-        <v>100</v>
+      <c r="E81">
+        <v>103.86070683328749</v>
       </c>
       <c r="F81">
-        <v>103.86070683328749</v>
-      </c>
-      <c r="G81">
         <v>1.3179148164723069</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C82">
         <v>0.593758517070336</v>
@@ -2897,22 +3191,19 @@
       <c r="D82">
         <v>0.47213019778871002</v>
       </c>
-      <c r="E82" t="s">
-        <v>100</v>
+      <c r="E82">
+        <v>103.86896644470291</v>
       </c>
       <c r="F82">
-        <v>103.86896644470291</v>
-      </c>
-      <c r="G82">
         <v>1.3328013522428701</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C83">
         <v>0.626062787719605</v>
@@ -2920,22 +3211,19 @@
       <c r="D83">
         <v>0.43291876400719598</v>
       </c>
-      <c r="E83" t="s">
-        <v>100</v>
+      <c r="E83">
+        <v>103.8710538041579</v>
       </c>
       <c r="F83">
-        <v>103.8710538041579</v>
-      </c>
-      <c r="G83">
         <v>1.3398672199419019</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C84">
         <v>0.69237155378915904</v>
@@ -2943,22 +3231,19 @@
       <c r="D84">
         <v>0.35736502574525297</v>
       </c>
-      <c r="E84" t="s">
-        <v>100</v>
+      <c r="E84">
+        <v>103.8847217321222</v>
       </c>
       <c r="F84">
-        <v>103.8847217321222</v>
-      </c>
-      <c r="G84">
         <v>1.360205623063266</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C85">
         <v>0.71787492535437103</v>
@@ -2966,22 +3251,19 @@
       <c r="D85">
         <v>0.329630109168084</v>
       </c>
-      <c r="E85" t="s">
-        <v>100</v>
+      <c r="E85">
+        <v>103.8929724009716</v>
       </c>
       <c r="F85">
-        <v>103.8929724009716</v>
-      </c>
-      <c r="G85">
         <v>1.371946116552726</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C86">
         <v>0.74082795976306304</v>
@@ -2989,22 +3271,19 @@
       <c r="D86">
         <v>0.30285156902461102</v>
       </c>
-      <c r="E86" t="s">
-        <v>100</v>
+      <c r="E86">
+        <v>103.8928838367306</v>
       </c>
       <c r="F86">
-        <v>103.8928838367306</v>
-      </c>
-      <c r="G86">
         <v>1.383409790989895</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C87">
         <v>0.76548121894276899</v>
@@ -3012,22 +3291,19 @@
       <c r="D87">
         <v>0.27607302888113699</v>
       </c>
-      <c r="E87" t="s">
-        <v>100</v>
+      <c r="E87">
+        <v>103.8957054566102</v>
       </c>
       <c r="F87">
-        <v>103.8957054566102</v>
-      </c>
-      <c r="G87">
         <v>1.392370843631531</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C88">
         <v>0.661767507910903</v>
@@ -3035,22 +3311,19 @@
       <c r="D88">
         <v>0.39179457735828999</v>
       </c>
-      <c r="E88" t="s">
-        <v>110</v>
+      <c r="E88">
+        <v>103.873546495734</v>
       </c>
       <c r="F88">
-        <v>103.873546495734</v>
-      </c>
-      <c r="G88">
         <v>1.349727699514359</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C89">
         <v>0.44158840006456601</v>
@@ -3058,22 +3331,19 @@
       <c r="D89">
         <v>0.88911032287993896</v>
       </c>
-      <c r="E89" t="s">
-        <v>110</v>
+      <c r="E89">
+        <v>103.8225316516256</v>
       </c>
       <c r="F89">
-        <v>103.8225316516256</v>
-      </c>
-      <c r="G89">
         <v>1.2652598837346909</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C90">
         <v>0.49939604227904899</v>
@@ -3081,22 +3351,19 @@
       <c r="D90">
         <v>0.74469748139192204</v>
       </c>
-      <c r="E90" t="s">
-        <v>113</v>
+      <c r="E90">
+        <v>103.84445854172969</v>
       </c>
       <c r="F90">
-        <v>103.84445854172969</v>
-      </c>
-      <c r="G90">
         <v>1.284736083637029</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C91">
         <v>0.57165559504715202</v>
@@ -3104,45 +3371,39 @@
       <c r="D91">
         <v>0.596459134169123</v>
       </c>
-      <c r="E91" t="s">
-        <v>113</v>
+      <c r="E91">
+        <v>103.8483043991358</v>
       </c>
       <c r="F91">
-        <v>103.8483043991358</v>
-      </c>
-      <c r="G91">
         <v>1.3076835365588511</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92">
+    <row r="92" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
-        <v>115</v>
-      </c>
-      <c r="C92">
+      <c r="B92" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C92" s="5">
         <v>0.44413873722108799</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="5">
         <v>0.78199616230604496</v>
       </c>
-      <c r="E92" t="s">
-        <v>116</v>
-      </c>
-      <c r="F92">
+      <c r="E92" s="5">
         <v>103.8403867870957</v>
       </c>
-      <c r="G92">
+      <c r="F92" s="5">
         <v>1.2802133538691181</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C93">
         <v>0.82498908592826503</v>
@@ -3150,22 +3411,19 @@
       <c r="D93">
         <v>0.208170302088758</v>
       </c>
-      <c r="E93" t="s">
-        <v>118</v>
+      <c r="E93">
+        <v>103.9023059966562</v>
       </c>
       <c r="F93">
-        <v>103.9023059966562</v>
-      </c>
-      <c r="G93">
         <v>1.405339576226845</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C94">
         <v>0.16445176238925399</v>
@@ -3173,22 +3431,19 @@
       <c r="D94">
         <v>0.554378571086522</v>
       </c>
-      <c r="E94" t="s">
-        <v>120</v>
+      <c r="E94">
+        <v>103.7497665649307</v>
       </c>
       <c r="F94">
-        <v>103.7497665649307</v>
-      </c>
-      <c r="G94">
         <v>1.3495200607327409</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C95">
         <v>0.16360165000374699</v>
@@ -3196,22 +3451,19 @@
       <c r="D95">
         <v>0.49125772646262</v>
       </c>
-      <c r="E95" t="s">
-        <v>120</v>
+      <c r="E95">
+        <v>103.75209299569801</v>
       </c>
       <c r="F95">
-        <v>103.75209299569801</v>
-      </c>
-      <c r="G95">
         <v>1.3586952612690939</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C96">
         <v>0.16445176238925399</v>
@@ -3219,22 +3471,19 @@
       <c r="D96">
         <v>0.34110662637243</v>
       </c>
-      <c r="E96" t="s">
-        <v>120</v>
+      <c r="E96">
+        <v>103.7473298800346</v>
       </c>
       <c r="F96">
-        <v>103.7473298800346</v>
-      </c>
-      <c r="G96">
         <v>1.398067768060026</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C97">
         <v>0.16360165000374699</v>
@@ -3242,22 +3491,19 @@
       <c r="D97">
         <v>0.26746564097787801</v>
       </c>
-      <c r="E97" t="s">
-        <v>120</v>
+      <c r="E97">
+        <v>103.7619406060964</v>
       </c>
       <c r="F97">
-        <v>103.7619406060964</v>
-      </c>
-      <c r="G97">
         <v>1.424852644661057</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C98">
         <v>0.19760614542403099</v>
@@ -3265,22 +3511,19 @@
       <c r="D98">
         <v>0.18330451481267601</v>
       </c>
-      <c r="E98" t="s">
-        <v>120</v>
+      <c r="E98">
+        <v>103.7738204510363</v>
       </c>
       <c r="F98">
-        <v>103.7738204510363</v>
-      </c>
-      <c r="G98">
         <v>1.432469522400065</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C99">
         <v>0.34297536334574402</v>
@@ -3288,22 +3531,19 @@
       <c r="D99">
         <v>0.165133362572462</v>
       </c>
-      <c r="E99" t="s">
-        <v>120</v>
+      <c r="E99">
+        <v>103.80054245816029</v>
       </c>
       <c r="F99">
-        <v>103.80054245816029</v>
-      </c>
-      <c r="G99">
         <v>1.440596285657938</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C100">
         <v>0.39228188170515499</v>
@@ -3311,22 +3551,19 @@
       <c r="D100">
         <v>0.165133362572462</v>
       </c>
-      <c r="E100" t="s">
-        <v>120</v>
+      <c r="E100">
+        <v>103.82010973575839</v>
       </c>
       <c r="F100">
-        <v>103.82010973575839</v>
-      </c>
-      <c r="G100">
         <v>1.448837319433129</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C101">
         <v>0.44413873722108799</v>
@@ -3334,22 +3571,19 @@
       <c r="D101">
         <v>0.16704611543985301</v>
       </c>
-      <c r="E101" t="s">
-        <v>120</v>
+      <c r="E101">
+        <v>103.82925464394749</v>
       </c>
       <c r="F101">
-        <v>103.82925464394749</v>
-      </c>
-      <c r="G101">
         <v>1.443511338844814</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C102">
         <v>0.49684570512252701</v>
@@ -3357,22 +3591,19 @@
       <c r="D102">
         <v>0.18521726768006699</v>
       </c>
-      <c r="E102" t="s">
-        <v>120</v>
+      <c r="E102">
+        <v>103.83478360318441</v>
       </c>
       <c r="F102">
-        <v>103.83478360318441</v>
-      </c>
-      <c r="G102">
         <v>1.429397167315948</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C103">
         <v>0.52404930145875395</v>
@@ -3380,22 +3611,19 @@
       <c r="D103">
         <v>0.22251594859419099</v>
       </c>
-      <c r="E103" t="s">
-        <v>120</v>
+      <c r="E103">
+        <v>103.8332310200385</v>
       </c>
       <c r="F103">
-        <v>103.8332310200385</v>
-      </c>
-      <c r="G103">
         <v>1.417869037116861</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C104">
         <v>0.53340053769933204</v>
@@ -3403,22 +3631,19 @@
       <c r="D104">
         <v>0.265552888110487</v>
       </c>
-      <c r="E104" t="s">
-        <v>120</v>
+      <c r="E104">
+        <v>103.8446457604343</v>
       </c>
       <c r="F104">
-        <v>103.8446457604343</v>
-      </c>
-      <c r="G104">
         <v>1.381953621306049</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C105">
         <v>0.53255042531382502</v>
@@ -3426,22 +3651,19 @@
       <c r="D105">
         <v>0.31050258049417501</v>
       </c>
-      <c r="E105" t="s">
-        <v>120</v>
+      <c r="E105">
+        <v>103.8498245724797</v>
       </c>
       <c r="F105">
-        <v>103.8498245724797</v>
-      </c>
-      <c r="G105">
         <v>1.369882375268169</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C106">
         <v>0.53170031292831799</v>
@@ -3449,22 +3671,19 @@
       <c r="D106">
         <v>0.393707330225681</v>
       </c>
-      <c r="E106" t="s">
-        <v>120</v>
+      <c r="E106">
+        <v>103.847440830591</v>
       </c>
       <c r="F106">
-        <v>103.847440830591</v>
-      </c>
-      <c r="G106">
         <v>1.3406721639431689</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C107">
         <v>0.53170031292831799</v>
@@ -3472,22 +3691,19 @@
       <c r="D107">
         <v>0.43578789330828199</v>
       </c>
-      <c r="E107" t="s">
-        <v>120</v>
+      <c r="E107">
+        <v>103.8477238043139</v>
       </c>
       <c r="F107">
-        <v>103.8477238043139</v>
-      </c>
-      <c r="G107">
         <v>1.332376442030206</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C108">
         <v>0.50959739090513401</v>
@@ -3495,22 +3711,19 @@
       <c r="D108">
         <v>0.48360671499305602</v>
       </c>
-      <c r="E108" t="s">
-        <v>120</v>
+      <c r="E108">
+        <v>103.8433397334763</v>
       </c>
       <c r="F108">
-        <v>103.8433397334763</v>
-      </c>
-      <c r="G108">
         <v>1.31989588603478</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C109">
         <v>0.47559289548485001</v>
@@ -3518,22 +3731,19 @@
       <c r="D109">
         <v>0.629932309348464</v>
       </c>
-      <c r="E109" t="s">
-        <v>120</v>
+      <c r="E109">
+        <v>103.8387655842814</v>
       </c>
       <c r="F109">
-        <v>103.8387655842814</v>
-      </c>
-      <c r="G109">
         <v>1.300436220589932</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C110">
         <v>0.65496660882684699</v>
@@ -3541,22 +3751,19 @@
       <c r="D110">
         <v>0.92736538022775805</v>
       </c>
-      <c r="E110" t="s">
-        <v>120</v>
+      <c r="E110">
+        <v>103.8615038787278</v>
       </c>
       <c r="F110">
-        <v>103.8615038787278</v>
-      </c>
-      <c r="G110">
         <v>1.273574804485931</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C111">
         <v>0.16275153761823999</v>
@@ -3564,22 +3771,19 @@
       <c r="D111">
         <v>0.415703988200677</v>
       </c>
-      <c r="E111" t="s">
-        <v>138</v>
+      <c r="E111">
+        <v>103.7445177987706</v>
       </c>
       <c r="F111">
-        <v>103.7445177987706</v>
-      </c>
-      <c r="G111">
         <v>1.3857361854031249</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C112">
         <v>0.53085020054281096</v>
@@ -3587,45 +3791,39 @@
       <c r="D112">
         <v>0.36023415504633899</v>
       </c>
-      <c r="E112" t="s">
-        <v>140</v>
+      <c r="E112">
+        <v>103.8502010819649</v>
       </c>
       <c r="F112">
-        <v>103.8502010819649</v>
-      </c>
-      <c r="G112">
         <v>1.351053219933295</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113">
+    <row r="113" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
-        <v>141</v>
-      </c>
-      <c r="C113">
+      <c r="B113" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113" s="5">
         <v>0.47644300787035698</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="5">
         <v>0.51803626660609303</v>
       </c>
-      <c r="E113" t="s">
-        <v>142</v>
-      </c>
-      <c r="F113">
+      <c r="E113" s="5">
         <v>103.8382423816355</v>
       </c>
-      <c r="G113">
+      <c r="F113" s="5">
         <v>1.3136172691498069</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C114">
         <v>0.16360165000374699</v>
@@ -3633,22 +3831,19 @@
       <c r="D114">
         <v>0.63853969725172399</v>
       </c>
-      <c r="E114" t="s">
-        <v>144</v>
+      <c r="E114">
+        <v>103.7426401629826</v>
       </c>
       <c r="F114">
-        <v>103.7426401629826</v>
-      </c>
-      <c r="G114">
         <v>1.3325262356481671</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C115">
         <v>0.60480997808192805</v>
@@ -3656,22 +3851,19 @@
       <c r="D115">
         <v>0.78390891517343597</v>
       </c>
-      <c r="E115" t="s">
-        <v>144</v>
+      <c r="E115">
+        <v>103.8518023338091</v>
       </c>
       <c r="F115">
-        <v>103.8518023338091</v>
-      </c>
-      <c r="G115">
         <v>1.293454825951323</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="C116">
         <v>0.60566009046743496</v>
@@ -3679,45 +3871,39 @@
       <c r="D116">
         <v>0.82407672538864696</v>
       </c>
-      <c r="E116" t="s">
-        <v>144</v>
+      <c r="E116">
+        <v>103.851621715866</v>
       </c>
       <c r="F116">
-        <v>103.851621715866</v>
-      </c>
-      <c r="G116">
         <v>1.285258281201247</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117">
+    <row r="117" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
-        <v>147</v>
-      </c>
-      <c r="C117">
+      <c r="B117" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117" s="5">
         <v>0.52064885191672605</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="5">
         <v>0.68062026033432499</v>
       </c>
-      <c r="E117" t="s">
-        <v>148</v>
-      </c>
-      <c r="F117">
+      <c r="E117" s="5">
         <v>103.8467879717855</v>
       </c>
-      <c r="G117">
+      <c r="F117" s="5">
         <v>1.298445092048172</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C118">
         <v>0.28601783351676902</v>
@@ -3725,22 +3911,19 @@
       <c r="D118">
         <v>0.16608973900615701</v>
       </c>
-      <c r="E118" t="s">
-        <v>150</v>
+      <c r="E118">
+        <v>103.7865080837622</v>
       </c>
       <c r="F118">
-        <v>103.7865080837622</v>
-      </c>
-      <c r="G118">
         <v>1.436673114687528</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C119">
         <v>0.44413873722108799</v>
@@ -3748,22 +3931,19 @@
       <c r="D119">
         <v>0.58306986409738604</v>
       </c>
-      <c r="E119" t="s">
-        <v>150</v>
+      <c r="E119">
+        <v>103.8306630989529</v>
       </c>
       <c r="F119">
-        <v>103.8306630989529</v>
-      </c>
-      <c r="G119">
         <v>1.3028576147489841</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="C120">
         <v>0.60480997808192805</v>
@@ -3771,22 +3951,19 @@
       <c r="D120">
         <v>0.88815394644624401</v>
       </c>
-      <c r="E120" t="s">
-        <v>150</v>
+      <c r="E120">
+        <v>103.8544700329541</v>
       </c>
       <c r="F120">
-        <v>103.8544700329541</v>
-      </c>
-      <c r="G120">
         <v>1.2773530329779259</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C121">
         <v>0.452639861076159</v>
@@ -3794,22 +3971,19 @@
       <c r="D121">
         <v>0.99526810702013702</v>
       </c>
-      <c r="E121" t="s">
-        <v>154</v>
+      <c r="E121">
+        <v>103.82096862792901</v>
       </c>
       <c r="F121">
-        <v>103.82096862792901</v>
-      </c>
-      <c r="G121">
         <v>1.25555920600891</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="C122">
         <v>0.24861288855445701</v>
@@ -3817,22 +3991,19 @@
       <c r="D122">
         <v>0.12400917592355599</v>
       </c>
-      <c r="E122" t="s">
-        <v>156</v>
+      <c r="E122">
+        <v>103.7854290806745</v>
       </c>
       <c r="F122">
-        <v>103.7854290806745</v>
-      </c>
-      <c r="G122">
         <v>1.4479365024965061</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C123">
         <v>0.311521205081981</v>
@@ -3840,22 +4011,19 @@
       <c r="D123">
         <v>0.19478103201702199</v>
       </c>
-      <c r="E123" t="s">
-        <v>156</v>
+      <c r="E123">
+        <v>103.79436521102041</v>
       </c>
       <c r="F123">
-        <v>103.79436521102041</v>
-      </c>
-      <c r="G123">
         <v>1.425843386909275</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="C124">
         <v>0.33362412710516598</v>
@@ -3863,22 +4031,19 @@
       <c r="D124">
         <v>0.22251594859419099</v>
       </c>
-      <c r="E124" t="s">
-        <v>156</v>
+      <c r="E124">
+        <v>103.8183906071381</v>
       </c>
       <c r="F124">
-        <v>103.8183906071381</v>
-      </c>
-      <c r="G124">
         <v>1.397820804057506</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C125">
         <v>0.35742727389936402</v>
@@ -3886,22 +4051,19 @@
       <c r="D125">
         <v>0.25025086517135903</v>
       </c>
-      <c r="E125" t="s">
-        <v>156</v>
+      <c r="E125">
+        <v>103.8358234520238</v>
       </c>
       <c r="F125">
-        <v>103.8358234520238</v>
-      </c>
-      <c r="G125">
         <v>1.3858909900868419</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C126">
         <v>0.38208053307906997</v>
@@ -3909,22 +4071,19 @@
       <c r="D126">
         <v>0.277985781748528</v>
       </c>
-      <c r="E126" t="s">
-        <v>156</v>
+      <c r="E126">
+        <v>103.8367959780974</v>
       </c>
       <c r="F126">
-        <v>103.8367959780974</v>
-      </c>
-      <c r="G126">
         <v>1.3712763229015379</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="C127">
         <v>0.40503356748776198</v>
@@ -3932,22 +4091,19 @@
       <c r="D127">
         <v>0.30572069832569698</v>
       </c>
-      <c r="E127" t="s">
-        <v>156</v>
+      <c r="E127">
+        <v>103.8336354139939</v>
       </c>
       <c r="F127">
-        <v>103.8336354139939</v>
-      </c>
-      <c r="G127">
         <v>1.364037182165615</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="C128">
         <v>0.42373603996891801</v>
@@ -3955,22 +4111,19 @@
       <c r="D128">
         <v>0.35449589644416701</v>
       </c>
-      <c r="E128" t="s">
-        <v>156</v>
+      <c r="E128">
+        <v>103.8318330090042</v>
       </c>
       <c r="F128">
-        <v>103.8318330090042</v>
-      </c>
-      <c r="G128">
         <v>1.3557365747065531</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C129">
         <v>0.42543626473993201</v>
@@ -3978,22 +4131,19 @@
       <c r="D129">
         <v>0.51612351373870302</v>
       </c>
-      <c r="E129" t="s">
-        <v>156</v>
+      <c r="E129">
+        <v>103.8194837777762</v>
       </c>
       <c r="F129">
-        <v>103.8194837777762</v>
-      </c>
-      <c r="G129">
         <v>1.3069359879223379</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C130">
         <v>0.42458615235442498</v>
@@ -4001,22 +4151,19 @@
       <c r="D130">
         <v>0.55055306535173998</v>
       </c>
-      <c r="E130" t="s">
-        <v>156</v>
+      <c r="E130">
+        <v>103.8306630989529</v>
       </c>
       <c r="F130">
-        <v>103.8306630989529</v>
-      </c>
-      <c r="G130">
         <v>1.3028576147489841</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="C131">
         <v>0.42458615235442498</v>
@@ -4024,22 +4171,19 @@
       <c r="D131">
         <v>0.62419405074629197</v>
       </c>
-      <c r="E131" t="s">
-        <v>156</v>
+      <c r="E131">
+        <v>103.833405504371</v>
       </c>
       <c r="F131">
-        <v>103.833405504371</v>
-      </c>
-      <c r="G131">
         <v>1.2965525945647349</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C132">
         <v>0.42543626473993201</v>
@@ -4047,22 +4191,19 @@
       <c r="D132">
         <v>0.66436186096150196</v>
       </c>
-      <c r="E132" t="s">
-        <v>156</v>
+      <c r="E132">
+        <v>103.8333695202785</v>
       </c>
       <c r="F132">
-        <v>103.8333695202785</v>
-      </c>
-      <c r="G132">
         <v>1.2888435633535369</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C133">
         <v>0.51384795283266904</v>
@@ -4070,22 +4211,19 @@
       <c r="D133">
         <v>0.80781832601582304</v>
       </c>
-      <c r="E133" t="s">
-        <v>156</v>
+      <c r="E133">
+        <v>103.8429163055429</v>
       </c>
       <c r="F133">
-        <v>103.8429163055429</v>
-      </c>
-      <c r="G133">
         <v>1.280191522380937</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C134">
         <v>0.56910525789063005</v>
@@ -4093,22 +4231,19 @@
       <c r="D134">
         <v>0.87285192350711605</v>
       </c>
-      <c r="E134" t="s">
-        <v>156</v>
+      <c r="E134">
+        <v>103.8518357073815</v>
       </c>
       <c r="F134">
-        <v>103.8518357073815</v>
-      </c>
-      <c r="G134">
         <v>1.2774620583356551</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="C135">
         <v>0.78248346665291002</v>
@@ -4116,22 +4251,19 @@
       <c r="D135">
         <v>0.85468077126690201</v>
       </c>
-      <c r="E135" t="s">
-        <v>156</v>
+      <c r="E135">
+        <v>103.867154122142</v>
       </c>
       <c r="F135">
-        <v>103.867154122142</v>
-      </c>
-      <c r="G135">
         <v>1.278303439968121</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C136">
         <v>0.84284144602391398</v>
@@ -4139,22 +4271,19 @@
       <c r="D136">
         <v>0.78773442090821799</v>
       </c>
-      <c r="E136" t="s">
-        <v>156</v>
+      <c r="E136">
+        <v>103.8734779049167</v>
       </c>
       <c r="F136">
-        <v>103.8734779049167</v>
-      </c>
-      <c r="G136">
         <v>1.2964594882816081</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="C137">
         <v>0.86664459281811301</v>
@@ -4162,22 +4291,19 @@
       <c r="D137">
         <v>0.76286863363213597</v>
       </c>
-      <c r="E137" t="s">
-        <v>156</v>
+      <c r="E137">
+        <v>103.88506921760499</v>
       </c>
       <c r="F137">
-        <v>103.88506921760499</v>
-      </c>
-      <c r="G137">
         <v>1.2983796827911389</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C138">
         <v>0.88874751484129699</v>
@@ -4185,22 +4311,19 @@
       <c r="D138">
         <v>0.735133717054967</v>
       </c>
-      <c r="E138" t="s">
-        <v>156</v>
+      <c r="E138">
+        <v>103.897045454194</v>
       </c>
       <c r="F138">
-        <v>103.897045454194</v>
-      </c>
-      <c r="G138">
         <v>1.2990386927771711</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C139">
         <v>0.91255066163549603</v>
@@ -4208,22 +4331,19 @@
       <c r="D139">
         <v>0.70835517691149397</v>
       </c>
-      <c r="E139" t="s">
-        <v>156</v>
+      <c r="E139">
+        <v>103.9059103666293</v>
       </c>
       <c r="F139">
-        <v>103.9059103666293</v>
-      </c>
-      <c r="G139">
         <v>1.3020932936434939</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="C140">
         <v>0.93635380842969396</v>
@@ -4231,22 +4351,19 @@
       <c r="D140">
         <v>0.68062026033432499</v>
       </c>
-      <c r="E140" t="s">
-        <v>156</v>
+      <c r="E140">
+        <v>103.91502013985659</v>
       </c>
       <c r="F140">
-        <v>103.91502013985659</v>
-      </c>
-      <c r="G140">
         <v>1.3068953217431261</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C141">
         <v>0.96185717999490705</v>
@@ -4254,22 +4371,19 @@
       <c r="D141">
         <v>0.65288534375715601</v>
       </c>
-      <c r="E141" t="s">
-        <v>156</v>
+      <c r="E141">
+        <v>103.9287926248893</v>
       </c>
       <c r="F141">
-        <v>103.9287926248893</v>
-      </c>
-      <c r="G141">
         <v>1.3088503155584581</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C142">
         <v>0.98140976486157006</v>
@@ -4277,22 +4391,19 @@
       <c r="D142">
         <v>0.63088868578215995</v>
       </c>
-      <c r="E142" t="s">
-        <v>156</v>
+      <c r="E142">
+        <v>103.9412617256652</v>
       </c>
       <c r="F142">
-        <v>103.9412617256652</v>
-      </c>
-      <c r="G142">
         <v>1.311898718691735</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="C143">
         <v>1.0035126868847499</v>
@@ -4300,22 +4411,19 @@
       <c r="D143">
         <v>0.60697927493977299</v>
       </c>
-      <c r="E143" t="s">
-        <v>156</v>
+      <c r="E143">
+        <v>103.9294042796889</v>
       </c>
       <c r="F143">
-        <v>103.9294042796889</v>
-      </c>
-      <c r="G143">
         <v>1.32407464586546</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C144">
         <v>1.03071628322098</v>
@@ -4323,22 +4431,19 @@
       <c r="D144">
         <v>0.57637522906151795</v>
       </c>
-      <c r="E144" t="s">
-        <v>192</v>
+      <c r="E144">
+        <v>103.9294042796889</v>
       </c>
       <c r="F144">
-        <v>103.9294042796889</v>
-      </c>
-      <c r="G144">
         <v>1.32407464586546</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C145">
         <v>0.42543626473993201</v>
@@ -4346,22 +4451,19 @@
       <c r="D145">
         <v>0.39944558882785403</v>
       </c>
-      <c r="E145" t="s">
-        <v>180</v>
+      <c r="E145">
+        <v>103.84038749923759</v>
       </c>
       <c r="F145">
-        <v>103.84038749923759</v>
-      </c>
-      <c r="G145">
         <v>1.338259729941808</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C146">
         <v>1.05555</v>
@@ -4369,22 +4471,19 @@
       <c r="D146">
         <v>0.54</v>
       </c>
-      <c r="E146" t="s">
-        <v>12</v>
+      <c r="E146">
+        <v>103.9649</v>
       </c>
       <c r="F146">
-        <v>103.9649</v>
-      </c>
-      <c r="G146">
         <v>1.3289</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C147">
         <v>0.24946300093996401</v>
@@ -4392,13 +4491,10 @@
       <c r="D147">
         <v>0.38333299999999998</v>
       </c>
-      <c r="E147" t="s">
-        <v>12</v>
+      <c r="E147">
+        <v>103.7692</v>
       </c>
       <c r="F147">
-        <v>103.7692</v>
-      </c>
-      <c r="G147">
         <v>1.3544</v>
       </c>
     </row>
@@ -4412,109 +4508,136 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="D1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="D3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="D4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="D6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="D7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="D8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>171</v>
+      </c>
+      <c r="D9" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4524,7 +4647,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -4557,6 +4680,9 @@
       <c r="C2" s="2">
         <v>5</v>
       </c>
+      <c r="D2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -4568,6 +4694,9 @@
       <c r="C3" s="2">
         <v>5</v>
       </c>
+      <c r="D3" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -4579,6 +4708,9 @@
       <c r="C4" s="2">
         <v>5</v>
       </c>
+      <c r="D4" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -4590,6 +4722,9 @@
       <c r="C5" s="2">
         <v>5</v>
       </c>
+      <c r="D5" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -4601,6 +4736,9 @@
       <c r="C6" s="2">
         <v>5</v>
       </c>
+      <c r="D6" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -4612,6 +4750,9 @@
       <c r="C7" s="2">
         <v>5</v>
       </c>
+      <c r="D7" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -4623,6 +4764,9 @@
       <c r="C8" s="2">
         <v>5</v>
       </c>
+      <c r="D8" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -4634,6 +4778,9 @@
       <c r="C9" s="2">
         <v>5</v>
       </c>
+      <c r="D9" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -4645,6 +4792,9 @@
       <c r="C10" s="2">
         <v>5</v>
       </c>
+      <c r="D10" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -4656,6 +4806,9 @@
       <c r="C11" s="2">
         <v>5</v>
       </c>
+      <c r="D11" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -4667,6 +4820,9 @@
       <c r="C12" s="2">
         <v>5</v>
       </c>
+      <c r="D12" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -4678,6 +4834,9 @@
       <c r="C13" s="2">
         <v>5</v>
       </c>
+      <c r="D13" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -4689,6 +4848,9 @@
       <c r="C14" s="2">
         <v>5</v>
       </c>
+      <c r="D14" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -4700,6 +4862,9 @@
       <c r="C15" s="2">
         <v>5</v>
       </c>
+      <c r="D15" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -4711,8 +4876,11 @@
       <c r="C16" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>111</v>
       </c>
@@ -4722,8 +4890,11 @@
       <c r="C17" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>11</v>
       </c>
@@ -4733,8 +4904,11 @@
       <c r="C18" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>145</v>
       </c>
@@ -4744,8 +4918,11 @@
       <c r="C19" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>22</v>
       </c>
@@ -4755,8 +4932,11 @@
       <c r="C20" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>12</v>
       </c>
@@ -4766,8 +4946,11 @@
       <c r="C21" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>13</v>
       </c>
@@ -4777,8 +4960,11 @@
       <c r="C22" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>24</v>
       </c>
@@ -4788,8 +4974,11 @@
       <c r="C23" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>14</v>
       </c>
@@ -4799,8 +4988,11 @@
       <c r="C24" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>15</v>
       </c>
@@ -4810,8 +5002,11 @@
       <c r="C25" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>16</v>
       </c>
@@ -4821,8 +5016,11 @@
       <c r="C26" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>17</v>
       </c>
@@ -4832,8 +5030,11 @@
       <c r="C27" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>18</v>
       </c>
@@ -4843,8 +5044,11 @@
       <c r="C28" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>19</v>
       </c>
@@ -4854,8 +5058,11 @@
       <c r="C29" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>88</v>
       </c>
@@ -4865,8 +5072,11 @@
       <c r="C30" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>119</v>
       </c>
@@ -4876,8 +5086,11 @@
       <c r="C31" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>25</v>
       </c>
@@ -4887,8 +5100,11 @@
       <c r="C32" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>121</v>
       </c>
@@ -4898,8 +5114,11 @@
       <c r="C33" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>117</v>
       </c>
@@ -4909,8 +5128,11 @@
       <c r="C34" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>122</v>
       </c>
@@ -4920,8 +5142,11 @@
       <c r="C35" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>123</v>
       </c>
@@ -4931,8 +5156,11 @@
       <c r="C36" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>124</v>
       </c>
@@ -4942,8 +5170,11 @@
       <c r="C37" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>125</v>
       </c>
@@ -4953,8 +5184,11 @@
       <c r="C38" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>126</v>
       </c>
@@ -4964,8 +5198,11 @@
       <c r="C39" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>127</v>
       </c>
@@ -4975,8 +5212,11 @@
       <c r="C40" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>145</v>
       </c>
@@ -4986,8 +5226,11 @@
       <c r="C41" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>50</v>
       </c>
@@ -4997,8 +5240,11 @@
       <c r="C42" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>129</v>
       </c>
@@ -5008,8 +5254,11 @@
       <c r="C43" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>130</v>
       </c>
@@ -5019,8 +5268,11 @@
       <c r="C44" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>118</v>
       </c>
@@ -5030,8 +5282,11 @@
       <c r="C45" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>131</v>
       </c>
@@ -5041,8 +5296,11 @@
       <c r="C46" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>132</v>
       </c>
@@ -5052,8 +5310,11 @@
       <c r="C47" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>91</v>
       </c>
@@ -5063,8 +5324,11 @@
       <c r="C48" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>133</v>
       </c>
@@ -5074,8 +5338,11 @@
       <c r="C49" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>134</v>
       </c>
@@ -5085,8 +5352,11 @@
       <c r="C50" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>119</v>
       </c>
@@ -5096,8 +5366,11 @@
       <c r="C51" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>135</v>
       </c>
@@ -5107,8 +5380,11 @@
       <c r="C52" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>136</v>
       </c>
@@ -5118,8 +5394,11 @@
       <c r="C53" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>137</v>
       </c>
@@ -5129,8 +5408,11 @@
       <c r="C54" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>138</v>
       </c>
@@ -5140,8 +5422,11 @@
       <c r="C55" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>139</v>
       </c>
@@ -5151,8 +5436,11 @@
       <c r="C56" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>140</v>
       </c>
@@ -5162,8 +5450,11 @@
       <c r="C57" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>141</v>
       </c>
@@ -5173,8 +5464,11 @@
       <c r="C58" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>142</v>
       </c>
@@ -5184,8 +5478,11 @@
       <c r="C59" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>143</v>
       </c>
@@ -5195,1277 +5492,3530 @@
       <c r="C60" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>144</v>
+        <v>113</v>
+      </c>
+      <c r="B61" s="2">
+        <v>93</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B62" s="2">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C62" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B63" s="2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C63" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B64" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C64" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B65" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C65" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B66" s="2">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C66" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B67" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C67" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B68" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C68" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C69" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C70" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B71" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B72" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B73" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B74" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B75" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C75" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B76" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C76" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B77" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B78" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C78" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B79" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C79" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B80" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C80" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B81" s="2">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C81" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B82" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C82" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B83" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C83" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B84" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C84" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B85" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C85" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="B86" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C86" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>109</v>
+        <v>76</v>
+      </c>
+      <c r="B87" s="2">
+        <v>52</v>
       </c>
       <c r="C87" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B88" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B89" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C89" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B90" s="2">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C90" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B91" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C91" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B92" s="2">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C92" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B93" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C93" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B94" s="2">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C94" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B95" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C95" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B96" s="2">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C96" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B97" s="2">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C97" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="B98" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C98" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B99" s="2">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="C99" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="B100" s="2">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C100" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B101" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C101" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B102" s="2">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C102" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B103" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C103" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B104" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C104" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B105" s="2">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="C105" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B106" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C106" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B107" s="2">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C107" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B108" s="2">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C108" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C109" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B110" s="2">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C110" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="B111" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C111" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B112" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C112" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B113" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C113" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B114" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C114" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B115" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C115" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B116" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C116" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B117" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C117" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C118" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D118" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="B119" s="2">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="C119" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D119" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>74</v>
+        <v>28</v>
+      </c>
+      <c r="B120" s="2">
+        <v>147</v>
       </c>
       <c r="C120" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D120" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="B121" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C121" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B122" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C122" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B123" s="2">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="C123" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="B124" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C124" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B125" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C125" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B126" s="2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C126" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B127" s="2">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C127" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="B128" s="2">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="C128" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="B129" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C129" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B130" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C130" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="B131" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C131" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B132" s="2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C132" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B133" s="2">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C133" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="B134" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C134" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B135" s="2">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="C135" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="B136" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C136" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B137" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C137" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B138" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="C138" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="B139" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C139" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B140" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C140" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B141" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C141" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B142" s="2">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C142" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B143" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C143" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B144" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C144" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B145" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C145" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B146" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C146" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B147" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C147" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B148" s="2">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C148" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B149" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C149" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B150" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C150" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B151" s="2">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C151" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B152" s="2">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="C152" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="B153" s="2">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="C153" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B154" s="2">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="C154" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D154" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B155" s="2">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="C155" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D155" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B156" s="2">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="C156" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D156" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>144</v>
+        <v>78</v>
+      </c>
+      <c r="B157" s="2">
+        <v>116</v>
       </c>
       <c r="C157" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D157" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="B158" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C158" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B159" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C159" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B160" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C160" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B161" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C161" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="B162" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C162" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B163" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C163" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B164" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C164" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B165" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C165" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B166" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C166" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B167" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C167" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B168" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C168" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B169" s="2">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C169" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B170" s="2">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="C170" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="D170" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B171" s="2">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C171" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
-        <v>86</v>
-      </c>
-      <c r="B172" s="2">
-        <v>92</v>
-      </c>
-      <c r="C172" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>92</v>
-      </c>
-      <c r="C173" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>75</v>
-      </c>
-      <c r="B174" s="2">
-        <v>49</v>
-      </c>
-      <c r="C174" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
-        <v>49</v>
-      </c>
-      <c r="B175" s="2">
-        <v>26</v>
-      </c>
-      <c r="C175" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
-        <v>26</v>
-      </c>
-      <c r="C176" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
-        <v>88</v>
-      </c>
-      <c r="B177" s="2">
-        <v>120</v>
-      </c>
-      <c r="C177" s="2">
         <v>8</v>
+      </c>
+      <c r="D171" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601FC106-E1E2-48FB-A7B2-5E1949209EA4}">
+  <dimension ref="A1:C177"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>23</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>24</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>25</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>26</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>29</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>31</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>32</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>33</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>34</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>35</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>36</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>37</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>38</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>39</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>40</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>41</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>42</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>43</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>44</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>45</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>46</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>47</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>48</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>49</v>
+      </c>
+      <c r="B56">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>49</v>
+      </c>
+      <c r="B57">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>50</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>50</v>
+      </c>
+      <c r="B59">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>51</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>52</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>53</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>54</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>55</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>56</v>
+      </c>
+      <c r="B65">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>57</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>58</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>59</v>
+      </c>
+      <c r="B68">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>60</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>61</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>62</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>63</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>64</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>65</v>
+      </c>
+      <c r="B74">
+        <v>3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>66</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>67</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>68</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
+      </c>
+      <c r="C77" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>69</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>70</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>71</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>72</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>73</v>
+      </c>
+      <c r="B82">
+        <v>3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>74</v>
+      </c>
+      <c r="B83">
+        <v>3</v>
+      </c>
+      <c r="C83" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>75</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>75</v>
+      </c>
+      <c r="B85">
+        <v>7</v>
+      </c>
+      <c r="C85" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>76</v>
+      </c>
+      <c r="B86">
+        <v>3</v>
+      </c>
+      <c r="C86" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>76</v>
+      </c>
+      <c r="B87">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>77</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>77</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>78</v>
+      </c>
+      <c r="B90">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>79</v>
+      </c>
+      <c r="B91">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>80</v>
+      </c>
+      <c r="B92">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>81</v>
+      </c>
+      <c r="B93">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>82</v>
+      </c>
+      <c r="B94">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>83</v>
+      </c>
+      <c r="B95">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>84</v>
+      </c>
+      <c r="B96">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>85</v>
+      </c>
+      <c r="B97">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>86</v>
+      </c>
+      <c r="B98">
+        <v>6</v>
+      </c>
+      <c r="C98" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>87</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+      <c r="C99" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>87</v>
+      </c>
+      <c r="B100">
+        <v>6</v>
+      </c>
+      <c r="C100" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>88</v>
+      </c>
+      <c r="B101">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>88</v>
+      </c>
+      <c r="B102">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>88</v>
+      </c>
+      <c r="B103">
+        <v>8</v>
+      </c>
+      <c r="C103" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>89</v>
+      </c>
+      <c r="B104">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>89</v>
+      </c>
+      <c r="B105">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>90</v>
+      </c>
+      <c r="B106">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>90</v>
+      </c>
+      <c r="B107">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>91</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>91</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="C109" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>91</v>
+      </c>
+      <c r="B110">
+        <v>6</v>
+      </c>
+      <c r="C110" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>92</v>
+      </c>
+      <c r="B111">
+        <v>6</v>
+      </c>
+      <c r="C111" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>93</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>94</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>95</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>96</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>97</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>98</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>99</v>
+      </c>
+      <c r="B118">
+        <v>2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>100</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>101</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>102</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>103</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>104</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>105</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>106</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>107</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+      <c r="C126" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>108</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>109</v>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>110</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>111</v>
+      </c>
+      <c r="B130">
+        <v>2</v>
+      </c>
+      <c r="C130" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>111</v>
+      </c>
+      <c r="B131">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>112</v>
+      </c>
+      <c r="B132">
+        <v>2</v>
+      </c>
+      <c r="C132" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>112</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>113</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>113</v>
+      </c>
+      <c r="B135">
+        <v>3</v>
+      </c>
+      <c r="C135" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>114</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>114</v>
+      </c>
+      <c r="B137">
+        <v>3</v>
+      </c>
+      <c r="C137" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>115</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>115</v>
+      </c>
+      <c r="B139">
+        <v>3</v>
+      </c>
+      <c r="C139" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>116</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>116</v>
+      </c>
+      <c r="B141">
+        <v>5</v>
+      </c>
+      <c r="C141" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>116</v>
+      </c>
+      <c r="B142">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>117</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>117</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>118</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>118</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>119</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>119</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>120</v>
+      </c>
+      <c r="B149">
+        <v>8</v>
+      </c>
+      <c r="C149" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>121</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>122</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>123</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>124</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>125</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>126</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>127</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>129</v>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="C157" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>130</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>131</v>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>132</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>133</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>134</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>135</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>136</v>
+      </c>
+      <c r="B164">
+        <v>1</v>
+      </c>
+      <c r="C164" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>137</v>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>138</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>139</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>140</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>141</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>142</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>143</v>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>144</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+      <c r="C172" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>144</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>145</v>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>145</v>
+      </c>
+      <c r="B175">
+        <v>5</v>
+      </c>
+      <c r="C175" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>146</v>
+      </c>
+      <c r="B176">
+        <v>4</v>
+      </c>
+      <c r="C176" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>147</v>
+      </c>
+      <c r="B177">
+        <v>4</v>
+      </c>
+      <c r="C177" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/singapore_stations.xlsx
+++ b/singapore_stations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uogcloud-my.sharepoint.com/personal/ac3005g_gre_ac_uk/Documents/COMP1938 - Advanced Programming/Coursework/comp1938_coursework/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="641" documentId="11_34FF6F5B68D74AE62BE44C2F3B03ACD57F4C09EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A50F6FD3-AEC9-4033-B542-EBA096DD23CD}"/>
+  <xr:revisionPtr revIDLastSave="745" documentId="11_34FF6F5B68D74AE62BE44C2F3B03ACD57F4C09EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D9B227-BB3C-425E-829C-11A4B5C9E72B}"/>
   <bookViews>
-    <workbookView xWindow="3732" yWindow="3120" windowWidth="17280" windowHeight="9960" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15660" yWindow="1725" windowWidth="21105" windowHeight="17985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="stations" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="384">
   <si>
     <t>line</t>
   </si>
@@ -1125,73 +1125,73 @@
     <t>top;left</t>
   </si>
   <si>
+    <t>top;right</t>
+  </si>
+  <si>
+    <t>bottom;left</t>
+  </si>
+  <si>
+    <t>CE1</t>
+  </si>
+  <si>
+    <t>station_line_id</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>NS28</t>
+  </si>
+  <si>
+    <t>middle</t>
+  </si>
+  <si>
+    <t>TE30</t>
+  </si>
+  <si>
+    <t>TE31</t>
+  </si>
+  <si>
+    <t>CE2</t>
+  </si>
+  <si>
+    <t>CC29</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>separate</t>
+  </si>
+  <si>
+    <t>STE1</t>
+  </si>
+  <si>
+    <t>STE2</t>
+  </si>
+  <si>
+    <t>is_triplet</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>connected_station</t>
+  </si>
+  <si>
+    <t>name_wrap</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>next_station_line_id</t>
+  </si>
+  <si>
     <t>bottom;right</t>
   </si>
   <si>
-    <t>top;right</t>
-  </si>
-  <si>
-    <t>bottom;left</t>
-  </si>
-  <si>
-    <t>CE1</t>
-  </si>
-  <si>
-    <t>station_line_id</t>
-  </si>
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>NS28</t>
-  </si>
-  <si>
-    <t>middle</t>
-  </si>
-  <si>
-    <t>TE30</t>
-  </si>
-  <si>
-    <t>TE31</t>
-  </si>
-  <si>
-    <t>CE2</t>
-  </si>
-  <si>
-    <t>CC29</t>
-  </si>
-  <si>
-    <t>offset</t>
-  </si>
-  <si>
-    <t>separate</t>
-  </si>
-  <si>
-    <t>special</t>
-  </si>
-  <si>
-    <t>STE1</t>
-  </si>
-  <si>
-    <t>STE2</t>
-  </si>
-  <si>
-    <t>is_triplet</t>
-  </si>
-  <si>
-    <t>station</t>
-  </si>
-  <si>
-    <t>connected_station</t>
-  </si>
-  <si>
-    <t>name_wrap</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>next_station_line_id</t>
+    <t>special,4</t>
   </si>
 </sst>
 </file>
@@ -1301,6 +1301,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1631,16 +1635,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1663,10 +1667,10 @@
         <v>186</v>
       </c>
       <c r="H1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1692,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.61586143909351998</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
         <v>0.72270082341692599</v>
@@ -1712,13 +1716,13 @@
         <v>1.296046213077239</v>
       </c>
       <c r="G3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1738,13 +1742,13 @@
         <v>1.2931288136602319</v>
       </c>
       <c r="G4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1770,7 +1774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1796,7 +1800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1822,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1848,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1874,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1900,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1926,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1952,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1978,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2004,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2030,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2056,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2082,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2108,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2134,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2160,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -2186,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2212,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -2222,8 +2226,8 @@
       <c r="C23" s="6">
         <v>0.34977626242980098</v>
       </c>
-      <c r="D23" s="6">
-        <v>0.47595570352349198</v>
+      <c r="D23">
+        <v>0.47691207995718798</v>
       </c>
       <c r="E23" s="6">
         <v>103.8159141457915</v>
@@ -2232,13 +2236,13 @@
         <v>1.32268461233639</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -2264,7 +2268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -2274,8 +2278,8 @@
       <c r="C25" s="6">
         <v>0.30216996884140301</v>
       </c>
-      <c r="D25" s="6">
-        <v>0.63758332081802804</v>
+      <c r="D25">
+        <v>0.63853969725172399</v>
       </c>
       <c r="E25" s="6">
         <v>103.7904491753026</v>
@@ -2290,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -2316,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2327,7 +2331,7 @@
         <v>1.1055261731456001</v>
       </c>
       <c r="D27">
-        <v>0.51038525513652999</v>
+        <v>0.51134163157022505</v>
       </c>
       <c r="E27">
         <v>103.9892766424138</v>
@@ -2342,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2368,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2376,7 +2380,7 @@
         <v>38</v>
       </c>
       <c r="C29">
-        <v>0.24861288855445701</v>
+        <v>0.24946300093996401</v>
       </c>
       <c r="D29">
         <v>0.35640864931155802</v>
@@ -2394,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2420,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2428,7 +2432,7 @@
         <v>40</v>
       </c>
       <c r="C31">
-        <v>0.25031311332547102</v>
+        <v>0.24946300093996401</v>
       </c>
       <c r="D31">
         <v>0.42335499967024098</v>
@@ -2446,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2472,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2498,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2524,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2550,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2570,13 +2574,13 @@
         <v>1.2822506642640741</v>
       </c>
       <c r="G36" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2599,10 +2603,10 @@
         <v>357</v>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2628,7 +2632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2654,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2680,7 +2684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2706,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2732,7 +2736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2758,7 +2762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2784,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2810,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2836,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2862,7 +2866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2888,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2914,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2934,13 +2938,13 @@
         <v>1.335950971715691</v>
       </c>
       <c r="G50" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2951,7 +2955,7 @@
         <v>0.42543626473993201</v>
       </c>
       <c r="D51">
-        <v>0.47499932708979697</v>
+        <v>0.47691207995718798</v>
       </c>
       <c r="E51">
         <v>103.82632257714459</v>
@@ -2960,13 +2964,13 @@
         <v>1.3209377434144121</v>
       </c>
       <c r="G51" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2992,7 +2996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3000,7 +3004,7 @@
         <v>63</v>
       </c>
       <c r="C53">
-        <v>1.0035126868847499</v>
+        <v>1.00521291165576</v>
       </c>
       <c r="D53">
         <v>0.43865702260936901</v>
@@ -3018,7 +3022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3038,13 +3042,13 @@
         <v>1.32407464586546</v>
       </c>
       <c r="G54" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3070,7 +3074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3096,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3122,7 +3126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3148,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3174,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3182,10 +3186,10 @@
         <v>70</v>
       </c>
       <c r="C60">
-        <v>0.50109626705006305</v>
+        <v>0.51109626699999999</v>
       </c>
       <c r="D60">
-        <v>0.84511700692994696</v>
+        <v>0.85511700700000004</v>
       </c>
       <c r="E60">
         <v>103.8469275802349</v>
@@ -3200,7 +3204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3226,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3252,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3278,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3304,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3330,7 +3334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3341,7 +3345,7 @@
         <v>0.219709067447215</v>
       </c>
       <c r="D66">
-        <v>0.63949607368541905</v>
+        <v>0.63853969725172399</v>
       </c>
       <c r="E66">
         <v>103.7655701161836</v>
@@ -3356,7 +3360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3382,7 +3386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3408,7 +3412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3434,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3460,7 +3464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3486,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3494,7 +3498,7 @@
         <v>82</v>
       </c>
       <c r="C72">
-        <v>3.5234679792176898E-2</v>
+        <v>3.43845674066698E-2</v>
       </c>
       <c r="D72">
         <v>0.47595570352349198</v>
@@ -3512,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3538,7 +3542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3564,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3590,7 +3594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3601,7 +3605,7 @@
         <v>0.98906077633113398</v>
       </c>
       <c r="D76">
-        <v>0.46161005701806002</v>
+        <v>0.46256643345175602</v>
       </c>
       <c r="E76">
         <v>103.9457230415822</v>
@@ -3613,10 +3617,10 @@
         <v>359</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3630,10 +3634,10 @@
         <v>0.393707330225681</v>
       </c>
       <c r="E77">
-        <v>103.9426536818783</v>
+        <v>103.9439</v>
       </c>
       <c r="F77">
-        <v>1.3541939276064221</v>
+        <v>1.355</v>
       </c>
       <c r="G77" t="s">
         <v>356</v>
@@ -3642,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3668,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3694,15 +3698,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
         <v>91</v>
       </c>
-      <c r="C80">
-        <v>0.57080548266164399</v>
+      <c r="C80" s="6">
+        <v>0.57165559504715202</v>
       </c>
       <c r="D80">
         <v>0.554378571086522</v>
@@ -3720,15 +3724,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
         <v>92</v>
       </c>
-      <c r="C81">
-        <v>0.56995537027613696</v>
+      <c r="C81" s="6">
+        <v>0.57165559504715202</v>
       </c>
       <c r="D81">
         <v>0.51325438443761595</v>
@@ -3746,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3772,7 +3776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3798,7 +3802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3824,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3850,7 +3854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3876,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3902,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3928,7 +3932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3948,13 +3952,13 @@
         <v>1.2652598837346909</v>
       </c>
       <c r="G89" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>89</v>
       </c>
@@ -3974,13 +3978,13 @@
         <v>1.284736083637029</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>90</v>
       </c>
@@ -4006,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -4032,7 +4036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4058,7 +4062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4066,7 +4070,7 @@
         <v>105</v>
       </c>
       <c r="C94">
-        <v>0.16445176238925399</v>
+        <v>0.16360165000374699</v>
       </c>
       <c r="D94">
         <v>0.554378571086522</v>
@@ -4084,7 +4088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4110,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4118,7 +4122,7 @@
         <v>108</v>
       </c>
       <c r="C96">
-        <v>0.16445176238925399</v>
+        <v>0.16360165000374699</v>
       </c>
       <c r="D96">
         <v>0.34110662637243</v>
@@ -4136,7 +4140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4162,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4188,7 +4192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4214,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4240,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4266,7 +4270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4292,7 +4296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4318,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4344,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4352,7 +4356,7 @@
         <v>117</v>
       </c>
       <c r="C105">
-        <v>0.53255042531382502</v>
+        <v>0.53340053769933204</v>
       </c>
       <c r="D105">
         <v>0.31050258049417501</v>
@@ -4370,7 +4374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4378,7 +4382,7 @@
         <v>118</v>
       </c>
       <c r="C106">
-        <v>0.53170031292831799</v>
+        <v>0.53340053769933204</v>
       </c>
       <c r="D106">
         <v>0.393707330225681</v>
@@ -4396,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -4404,7 +4408,7 @@
         <v>119</v>
       </c>
       <c r="C107">
-        <v>0.53170031292831799</v>
+        <v>0.53340053769933204</v>
       </c>
       <c r="D107">
         <v>0.43578789330828199</v>
@@ -4422,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -4448,7 +4452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -4474,7 +4478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4500,7 +4504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4508,7 +4512,7 @@
         <v>123</v>
       </c>
       <c r="C111">
-        <v>0.16275153761823999</v>
+        <v>0.16360165000374699</v>
       </c>
       <c r="D111">
         <v>0.415703988200677</v>
@@ -4526,15 +4530,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>111</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C112" s="6">
-        <v>0.53085020054281096</v>
+      <c r="C112">
+        <v>0.53340053769933204</v>
       </c>
       <c r="D112" s="6">
         <v>0.36023415504633899</v>
@@ -4546,13 +4550,13 @@
         <v>1.351053219933295</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -4572,13 +4576,13 @@
         <v>1.3136172691498069</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4604,15 +4608,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
         <v>127</v>
       </c>
-      <c r="C115">
-        <v>0.60480997808192805</v>
+      <c r="C115" s="6">
+        <v>0.60566009046743496</v>
       </c>
       <c r="D115">
         <v>0.78390891517343597</v>
@@ -4630,7 +4634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -4650,13 +4654,13 @@
         <v>1.285258281201247</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="H116" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -4676,13 +4680,13 @@
         <v>1.298445092048172</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H117" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4708,24 +4712,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>118</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C119" s="6">
-        <v>0.44413873722108799</v>
+      <c r="C119">
+        <v>0.42543626473993201</v>
       </c>
       <c r="D119" s="6">
         <v>0.58306986409738604</v>
       </c>
-      <c r="E119" s="6">
-        <v>103.8306630989529</v>
-      </c>
-      <c r="F119" s="6">
-        <v>1.3028576147489841</v>
+      <c r="E119">
+        <v>103.8258</v>
+      </c>
+      <c r="F119">
+        <v>1.3026</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>356</v>
@@ -4734,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -4754,13 +4758,13 @@
         <v>1.2773530329779259</v>
       </c>
       <c r="G120" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -4812,7 +4816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4838,7 +4842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4864,7 +4868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -4890,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4916,7 +4920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4942,7 +4946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4950,7 +4954,7 @@
         <v>142</v>
       </c>
       <c r="C128">
-        <v>0.42373603996891801</v>
+        <v>0.42543626473993201</v>
       </c>
       <c r="D128">
         <v>0.35449589644416701</v>
@@ -4968,7 +4972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>129</v>
       </c>
@@ -4994,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>130</v>
       </c>
@@ -5002,7 +5006,7 @@
         <v>144</v>
       </c>
       <c r="C130">
-        <v>0.42458615235442498</v>
+        <v>0.42543626473993201</v>
       </c>
       <c r="D130">
         <v>0.55055306535173998</v>
@@ -5020,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>131</v>
       </c>
@@ -5028,7 +5032,7 @@
         <v>145</v>
       </c>
       <c r="C131">
-        <v>0.42458615235442498</v>
+        <v>0.42543626473993201</v>
       </c>
       <c r="D131">
         <v>0.62419405074629197</v>
@@ -5046,7 +5050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>132</v>
       </c>
@@ -5072,7 +5076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>133</v>
       </c>
@@ -5080,10 +5084,10 @@
         <v>147</v>
       </c>
       <c r="C133">
-        <v>0.51384795283266904</v>
+        <v>0.51555499999999999</v>
       </c>
       <c r="D133">
-        <v>0.80781832601582304</v>
+        <v>0.82312034895495101</v>
       </c>
       <c r="E133">
         <v>103.8429163055429</v>
@@ -5098,7 +5102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>134</v>
       </c>
@@ -5124,7 +5128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>135</v>
       </c>
@@ -5150,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>136</v>
       </c>
@@ -5176,7 +5180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>137</v>
       </c>
@@ -5202,7 +5206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>138</v>
       </c>
@@ -5228,7 +5232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>139</v>
       </c>
@@ -5254,7 +5258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>140</v>
       </c>
@@ -5280,7 +5284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>141</v>
       </c>
@@ -5306,7 +5310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>142</v>
       </c>
@@ -5332,7 +5336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>143</v>
       </c>
@@ -5358,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>144</v>
       </c>
@@ -5378,13 +5382,13 @@
         <v>1.32407464586546</v>
       </c>
       <c r="G144" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="H144" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>145</v>
       </c>
@@ -5410,7 +5414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>146</v>
       </c>
@@ -5430,13 +5434,13 @@
         <v>1.3289</v>
       </c>
       <c r="G146" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H146" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>147</v>
       </c>
@@ -5462,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>148</v>
       </c>
@@ -5476,16 +5480,16 @@
         <v>0.40996572959850403</v>
       </c>
       <c r="E148">
-        <v>103.9426536818783</v>
+        <v>103.9439</v>
       </c>
       <c r="F148">
-        <v>1.3541939276064221</v>
+        <v>1.355</v>
       </c>
       <c r="H148" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -5521,12 +5525,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="24.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5540,10 +5544,10 @@
         <v>172</v>
       </c>
       <c r="E1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5560,7 +5564,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5577,7 +5581,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5594,7 +5598,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5611,7 +5615,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5628,7 +5632,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5645,7 +5649,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5662,7 +5666,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5687,14 +5691,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601FC106-E1E2-48FB-A7B2-5E1949209EA4}">
   <dimension ref="A1:D178"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5708,7 +5712,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5722,7 +5726,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5736,7 +5740,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5750,7 +5754,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5764,7 +5768,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5778,7 +5782,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5792,7 +5796,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5806,7 +5810,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5820,7 +5824,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5834,7 +5838,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5848,7 +5852,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5862,7 +5866,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5876,7 +5880,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5890,7 +5894,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5904,7 +5908,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5918,7 +5922,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5932,7 +5936,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5946,7 +5950,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5960,7 +5964,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5974,7 +5978,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5988,7 +5992,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6002,7 +6006,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6016,7 +6020,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6030,7 +6034,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6044,7 +6048,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6058,7 +6062,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6072,7 +6076,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6086,7 +6090,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6100,7 +6104,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6114,7 +6118,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6128,7 +6132,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6139,10 +6143,10 @@
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6156,7 +6160,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6170,7 +6174,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6184,7 +6188,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6198,7 +6202,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6212,7 +6216,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6226,7 +6230,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6240,7 +6244,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6254,7 +6258,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6268,7 +6272,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6282,7 +6286,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6296,7 +6300,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6310,7 +6314,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6324,7 +6328,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6338,7 +6342,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6352,7 +6356,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6366,7 +6370,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6380,7 +6384,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6394,7 +6398,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6408,7 +6412,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6422,7 +6426,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6436,7 +6440,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6450,7 +6454,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6464,7 +6468,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6478,7 +6482,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6492,7 +6496,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6506,7 +6510,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6520,7 +6524,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6534,7 +6538,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6548,7 +6552,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6562,7 +6566,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6576,7 +6580,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6590,7 +6594,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6604,7 +6608,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6618,7 +6622,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6632,7 +6636,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6646,7 +6650,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6660,7 +6664,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6674,7 +6678,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6688,7 +6692,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6702,7 +6706,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6716,7 +6720,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6730,7 +6734,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6744,7 +6748,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6758,7 +6762,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6772,7 +6776,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6786,7 +6790,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6800,7 +6804,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6814,7 +6818,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6828,7 +6832,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6842,7 +6846,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6856,7 +6860,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6870,7 +6874,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6884,7 +6888,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6898,7 +6902,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6926,7 +6930,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6940,7 +6944,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6954,7 +6958,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6968,7 +6972,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6982,7 +6986,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6996,7 +7000,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7010,7 +7014,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7024,7 +7028,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7038,7 +7042,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7052,7 +7056,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7066,7 +7070,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7080,7 +7084,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7094,7 +7098,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7105,10 +7109,10 @@
         <v>5</v>
       </c>
       <c r="D101" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7122,7 +7126,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7133,10 +7137,10 @@
         <v>8</v>
       </c>
       <c r="D103" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7150,7 +7154,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7164,7 +7168,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7178,7 +7182,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7192,7 +7196,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7206,7 +7210,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7220,7 +7224,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7234,7 +7238,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7248,7 +7252,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7262,7 +7266,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7276,7 +7280,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7290,7 +7294,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7304,7 +7308,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7318,7 +7322,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7332,7 +7336,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7346,7 +7350,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7360,7 +7364,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7374,7 +7378,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7388,7 +7392,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7416,7 +7420,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7430,7 +7434,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7444,7 +7448,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7458,7 +7462,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7472,7 +7476,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7483,10 +7487,10 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7500,7 +7504,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7514,7 +7518,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7528,7 +7532,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7556,7 +7560,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7570,7 +7574,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7584,7 +7588,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7598,7 +7602,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7612,7 +7616,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7626,7 +7630,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7640,7 +7644,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7654,7 +7658,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7668,7 +7672,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7682,7 +7686,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7696,7 +7700,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7710,7 +7714,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7724,7 +7728,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7738,7 +7742,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7752,7 +7756,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7766,7 +7770,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7777,10 +7781,10 @@
         <v>8</v>
       </c>
       <c r="D149" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7794,7 +7798,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7808,7 +7812,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7822,7 +7826,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7836,7 +7840,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7850,7 +7854,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7864,7 +7868,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7878,7 +7882,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7892,7 +7896,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7906,7 +7910,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7920,7 +7924,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7934,7 +7938,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -7948,7 +7952,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -7962,7 +7966,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -7976,7 +7980,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -7990,7 +7994,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8004,7 +8008,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8018,7 +8022,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8032,7 +8036,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8046,7 +8050,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8060,7 +8064,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8074,7 +8078,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8085,10 +8089,10 @@
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8099,10 +8103,10 @@
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -8116,7 +8120,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8130,7 +8134,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8144,7 +8148,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8158,7 +8162,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8172,7 +8176,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -8183,7 +8187,7 @@
         <v>5</v>
       </c>
       <c r="D178" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -8197,22 +8201,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G173"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -8221,13 +8225,13 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>140</v>
       </c>
@@ -8249,7 +8253,7 @@
         <v>Bras Basah</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8271,7 +8275,7 @@
         <v>Esplanade</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8293,7 +8297,7 @@
         <v>Promenade</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>21</v>
       </c>
@@ -8315,7 +8319,7 @@
         <v>Nicoll Highway</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -8337,7 +8341,7 @@
         <v>Stadium</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -8359,7 +8363,7 @@
         <v>Mountbatten</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -8381,7 +8385,7 @@
         <v>Dakota</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -8403,7 +8407,7 @@
         <v>Paya Lebar</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>27</v>
       </c>
@@ -8425,7 +8429,7 @@
         <v>MacPherson</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>23</v>
       </c>
@@ -8447,7 +8451,7 @@
         <v>Tai Seng</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -8469,7 +8473,7 @@
         <v>Bartley</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -8491,7 +8495,7 @@
         <v>Serangoon</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>98</v>
       </c>
@@ -8513,7 +8517,7 @@
         <v>Lorong Chuan</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>10</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>Bishan</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>130</v>
       </c>
@@ -8557,7 +8561,7 @@
         <v>Marymount</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>11</v>
       </c>
@@ -8579,7 +8583,7 @@
         <v>Caldecott</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>174</v>
       </c>
@@ -8601,7 +8605,7 @@
         <v>Botanic Gardens</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>Farrer Road</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>12</v>
       </c>
@@ -8645,7 +8649,7 @@
         <v>Holland Village</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>13</v>
       </c>
@@ -8667,7 +8671,7 @@
         <v>Buona Vista</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>29</v>
       </c>
@@ -8689,7 +8693,7 @@
         <v>one-north</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>14</v>
       </c>
@@ -8711,7 +8715,7 @@
         <v>Kent Ridge</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>15</v>
       </c>
@@ -8733,7 +8737,7 @@
         <v>Haw Par Villa</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>16</v>
       </c>
@@ -8755,7 +8759,7 @@
         <v>Pasir Panjang</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>17</v>
       </c>
@@ -8777,7 +8781,7 @@
         <v>Labrador Park</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>18</v>
       </c>
@@ -8799,7 +8803,7 @@
         <v>Telok Blangah</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>19</v>
       </c>
@@ -8821,7 +8825,7 @@
         <v>HarbourFront</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>100</v>
       </c>
@@ -8843,7 +8847,7 @@
         <v>Marina Bay</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>177</v>
       </c>
@@ -8865,7 +8869,7 @@
         <v>Bayfront</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>31</v>
       </c>
@@ -8887,7 +8891,7 @@
         <v>Promenade</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>149</v>
       </c>
@@ -8909,7 +8913,7 @@
         <v>Woodlands</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>142</v>
       </c>
@@ -8931,7 +8935,7 @@
         <v>Woodlands South</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>150</v>
       </c>
@@ -8953,7 +8957,7 @@
         <v>Springleaf</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>151</v>
       </c>
@@ -8975,7 +8979,7 @@
         <v>Lentor</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>152</v>
       </c>
@@ -8997,7 +9001,7 @@
         <v>Mayflower</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>153</v>
       </c>
@@ -9019,7 +9023,7 @@
         <v>Bright Hill</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>154</v>
       </c>
@@ -9041,7 +9045,7 @@
         <v>Upper Thomson</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>155</v>
       </c>
@@ -9063,7 +9067,7 @@
         <v>Caldecott</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>173</v>
       </c>
@@ -9085,7 +9089,7 @@
         <v>Stevens</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>57</v>
       </c>
@@ -9107,7 +9111,7 @@
         <v>Napier</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>156</v>
       </c>
@@ -9129,7 +9133,7 @@
         <v>Orchard Boulevard</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>157</v>
       </c>
@@ -9151,7 +9155,7 @@
         <v>Orchard</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>144</v>
       </c>
@@ -9173,7 +9177,7 @@
         <v>Great World</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>158</v>
       </c>
@@ -9195,7 +9199,7 @@
         <v>Havelock</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>159</v>
       </c>
@@ -9217,7 +9221,7 @@
         <v>Outram Park</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>107</v>
       </c>
@@ -9239,7 +9243,7 @@
         <v>Maxwell</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>160</v>
       </c>
@@ -9261,7 +9265,7 @@
         <v>Shenton Way</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>161</v>
       </c>
@@ -9283,7 +9287,7 @@
         <v>Marina Bay</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>146</v>
       </c>
@@ -9305,7 +9309,7 @@
         <v>Gardens by the Bay</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>162</v>
       </c>
@@ -9327,7 +9331,7 @@
         <v>Tanjong Rhu</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>163</v>
       </c>
@@ -9349,7 +9353,7 @@
         <v>Katong Park</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>164</v>
       </c>
@@ -9371,7 +9375,7 @@
         <v>Tanjong Katong</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>165</v>
       </c>
@@ -9393,7 +9397,7 @@
         <v>Marine Parade</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>166</v>
       </c>
@@ -9415,7 +9419,7 @@
         <v>Marine Terrace</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>167</v>
       </c>
@@ -9437,7 +9441,7 @@
         <v>Siglap</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>168</v>
       </c>
@@ -9459,7 +9463,7 @@
         <v>Bayshore</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>169</v>
       </c>
@@ -9481,7 +9485,7 @@
         <v>Bedok South</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>170</v>
       </c>
@@ -9503,7 +9507,7 @@
         <v>Sungei Bedok</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>133</v>
       </c>
@@ -9525,12 +9529,12 @@
         <v>Bukit Batok</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>111</v>
       </c>
       <c r="B61">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C61" s="2">
         <v>2</v>
@@ -9544,15 +9548,15 @@
       </c>
       <c r="G61" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(B61, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>Choa Chu Kang</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Bukit Gombak</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
+        <v>112</v>
+      </c>
+      <c r="B62">
         <v>128</v>
-      </c>
-      <c r="B62">
-        <v>113</v>
       </c>
       <c r="C62" s="2">
         <v>2</v>
@@ -9562,14 +9566,14 @@
       </c>
       <c r="F62" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(A62, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>Choa Chu Kang</v>
+        <v>Bukit Gombak</v>
       </c>
       <c r="G62" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(B62, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>Yew Tee</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Choa Chu Kang</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>113</v>
       </c>
@@ -9591,7 +9595,7 @@
         <v>Kranji</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>114</v>
       </c>
@@ -9613,7 +9617,7 @@
         <v>Marsiling</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>115</v>
       </c>
@@ -9635,7 +9639,7 @@
         <v>Woodlands</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>143</v>
       </c>
@@ -9657,7 +9661,7 @@
         <v>Admiralty</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>116</v>
       </c>
@@ -9679,7 +9683,7 @@
         <v>Sembawang</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>117</v>
       </c>
@@ -9701,7 +9705,7 @@
         <v>Canberra</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>118</v>
       </c>
@@ -9723,7 +9727,7 @@
         <v>Yishun</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>119</v>
       </c>
@@ -9745,7 +9749,7 @@
         <v>Khatib</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>120</v>
       </c>
@@ -9767,7 +9771,7 @@
         <v>Yio Chu Kang</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>121</v>
       </c>
@@ -9789,7 +9793,7 @@
         <v>Ang Mo Kio</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>122</v>
       </c>
@@ -9811,7 +9815,7 @@
         <v>Bishan</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>129</v>
       </c>
@@ -9833,7 +9837,7 @@
         <v>Braddell</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>123</v>
       </c>
@@ -9855,7 +9859,7 @@
         <v>Toa Payoh</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>124</v>
       </c>
@@ -9877,7 +9881,7 @@
         <v>Novena</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>125</v>
       </c>
@@ -9899,7 +9903,7 @@
         <v>Newton</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>131</v>
       </c>
@@ -9921,7 +9925,7 @@
         <v>Orchard</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>145</v>
       </c>
@@ -9943,7 +9947,7 @@
         <v>Somerset</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>126</v>
       </c>
@@ -9965,7 +9969,7 @@
         <v>Dhoby Ghaut</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>139</v>
       </c>
@@ -9987,7 +9991,7 @@
         <v>City Hall</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>135</v>
       </c>
@@ -10009,7 +10013,7 @@
         <v>Raffles Place</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>137</v>
       </c>
@@ -10031,7 +10035,7 @@
         <v>Marina Bay</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>147</v>
       </c>
@@ -10053,7 +10057,7 @@
         <v>Marina South Pier</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>59</v>
       </c>
@@ -10075,7 +10079,7 @@
         <v>Tampines</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -10097,7 +10101,7 @@
         <v>Simei</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>60</v>
       </c>
@@ -10119,7 +10123,7 @@
         <v>Tanah Merah</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>83</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>Bedok</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>61</v>
       </c>
@@ -10163,7 +10167,7 @@
         <v>Kembangan</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>62</v>
       </c>
@@ -10185,7 +10189,7 @@
         <v>Eunos</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>63</v>
       </c>
@@ -10207,7 +10211,7 @@
         <v>Paya Lebar</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>26</v>
       </c>
@@ -10229,7 +10233,7 @@
         <v>Aljunied</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>64</v>
       </c>
@@ -10251,7 +10255,7 @@
         <v>Kallang</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>65</v>
       </c>
@@ -10273,7 +10277,7 @@
         <v>Lavender</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>66</v>
       </c>
@@ -10295,7 +10299,7 @@
         <v>Bugis</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>87</v>
       </c>
@@ -10317,7 +10321,7 @@
         <v>City Hall</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>136</v>
       </c>
@@ -10339,7 +10343,7 @@
         <v>Raffles Place</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>138</v>
       </c>
@@ -10361,7 +10365,7 @@
         <v>Tanjong Pagar</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>67</v>
       </c>
@@ -10383,7 +10387,7 @@
         <v>Outram Park</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>108</v>
       </c>
@@ -10405,7 +10409,7 @@
         <v>Tiong Bahru</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>68</v>
       </c>
@@ -10427,7 +10431,7 @@
         <v>Redhill</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>69</v>
       </c>
@@ -10449,7 +10453,7 @@
         <v>Queenstown</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>70</v>
       </c>
@@ -10471,7 +10475,7 @@
         <v>Commonwealth</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>71</v>
       </c>
@@ -10493,7 +10497,7 @@
         <v>Buona Vista</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>28</v>
       </c>
@@ -10515,7 +10519,7 @@
         <v>Dover</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>72</v>
       </c>
@@ -10537,7 +10541,7 @@
         <v>Clementi</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>73</v>
       </c>
@@ -10559,7 +10563,7 @@
         <v>Jurong East</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>134</v>
       </c>
@@ -10581,7 +10585,7 @@
         <v>Chinese Garden</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>74</v>
       </c>
@@ -10603,7 +10607,7 @@
         <v>Lakeside</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>75</v>
       </c>
@@ -10625,7 +10629,7 @@
         <v>Boon Lay</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>76</v>
       </c>
@@ -10647,7 +10651,7 @@
         <v>Pioneer</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>77</v>
       </c>
@@ -10669,7 +10673,7 @@
         <v>Joo Koon</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>78</v>
       </c>
@@ -10691,7 +10695,7 @@
         <v>Gul Circle</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>79</v>
       </c>
@@ -10713,7 +10717,7 @@
         <v>Tuas Crescent</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>80</v>
       </c>
@@ -10735,7 +10739,7 @@
         <v>Tuas West Road</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>81</v>
       </c>
@@ -10757,7 +10761,7 @@
         <v>Tuas Link</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1</v>
       </c>
@@ -10779,7 +10783,7 @@
         <v>Cashew</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>33</v>
       </c>
@@ -10801,7 +10805,7 @@
         <v>Hillview</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>34</v>
       </c>
@@ -10823,7 +10827,7 @@
         <v>Hume</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>176</v>
       </c>
@@ -10845,7 +10849,7 @@
         <v>Beauty World</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>35</v>
       </c>
@@ -10867,7 +10871,7 @@
         <v>King Albert Park</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>36</v>
       </c>
@@ -10889,7 +10893,7 @@
         <v>Sixth Avenue</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>37</v>
       </c>
@@ -10911,7 +10915,7 @@
         <v>Tan Kah Kee</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>38</v>
       </c>
@@ -10933,7 +10937,7 @@
         <v>Botanic Gardens</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>24</v>
       </c>
@@ -10955,7 +10959,7 @@
         <v>Stevens</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>58</v>
       </c>
@@ -10977,7 +10981,7 @@
         <v>Newton</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>132</v>
       </c>
@@ -10999,7 +11003,7 @@
         <v>Little India</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>105</v>
       </c>
@@ -11021,7 +11025,7 @@
         <v>Rochor</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>39</v>
       </c>
@@ -11043,7 +11047,7 @@
         <v>Bugis</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>88</v>
       </c>
@@ -11065,7 +11069,7 @@
         <v>Promenade</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>20</v>
       </c>
@@ -11087,7 +11091,7 @@
         <v>Bayfront</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>30</v>
       </c>
@@ -11109,7 +11113,7 @@
         <v>Downtown</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>40</v>
       </c>
@@ -11131,7 +11135,7 @@
         <v>Telok Ayer</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>41</v>
       </c>
@@ -11153,7 +11157,7 @@
         <v>Chinatown</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>103</v>
       </c>
@@ -11175,7 +11179,7 @@
         <v>Fort Canning</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>42</v>
       </c>
@@ -11197,7 +11201,7 @@
         <v>Bencoolen</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>43</v>
       </c>
@@ -11219,7 +11223,7 @@
         <v>Jalan Besar</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>44</v>
       </c>
@@ -11241,7 +11245,7 @@
         <v>Bendemeer</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>45</v>
       </c>
@@ -11263,7 +11267,7 @@
         <v>Geylang Bahru</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>46</v>
       </c>
@@ -11285,7 +11289,7 @@
         <v>Mattar</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>47</v>
       </c>
@@ -11307,7 +11311,7 @@
         <v>MacPherson</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>22</v>
       </c>
@@ -11329,7 +11333,7 @@
         <v>Ubi</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>48</v>
       </c>
@@ -11351,7 +11355,7 @@
         <v>Kaki Bukit</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>49</v>
       </c>
@@ -11373,7 +11377,7 @@
         <v>Bedok North</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>50</v>
       </c>
@@ -11395,7 +11399,7 @@
         <v>Bedok Reservoir</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>51</v>
       </c>
@@ -11417,7 +11421,7 @@
         <v>Tampines West</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>52</v>
       </c>
@@ -11439,7 +11443,7 @@
         <v>Tampines</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>86</v>
       </c>
@@ -11461,7 +11465,7 @@
         <v>Tampines East</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>53</v>
       </c>
@@ -11483,7 +11487,7 @@
         <v>Upper Changi</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>54</v>
       </c>
@@ -11505,7 +11509,7 @@
         <v>Expo</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>55</v>
       </c>
@@ -11527,7 +11531,7 @@
         <v>Xilin</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>175</v>
       </c>
@@ -11549,7 +11553,7 @@
         <v>Sungei Bedok</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>101</v>
       </c>
@@ -11571,7 +11575,7 @@
         <v>Outram Park</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>109</v>
       </c>
@@ -11593,7 +11597,7 @@
         <v>Chinatown</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>104</v>
       </c>
@@ -11615,7 +11619,7 @@
         <v>Clarke Quay</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>89</v>
       </c>
@@ -11637,7 +11641,7 @@
         <v>Dhoby Ghaut</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>141</v>
       </c>
@@ -11659,7 +11663,7 @@
         <v>Little India</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>106</v>
       </c>
@@ -11681,7 +11685,7 @@
         <v>Farrer Park</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>90</v>
       </c>
@@ -11703,7 +11707,7 @@
         <v>Boon Keng</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>91</v>
       </c>
@@ -11725,7 +11729,7 @@
         <v>Potong Pasir</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>92</v>
       </c>
@@ -11747,7 +11751,7 @@
         <v>Woodleigh</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>93</v>
       </c>
@@ -11769,7 +11773,7 @@
         <v>Serangoon</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>99</v>
       </c>
@@ -11791,7 +11795,7 @@
         <v>Kovan</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>94</v>
       </c>
@@ -11813,7 +11817,7 @@
         <v>Hougang</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>95</v>
       </c>
@@ -11835,7 +11839,7 @@
         <v>Buangkok</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>96</v>
       </c>
@@ -11857,7 +11861,7 @@
         <v>Sengkang</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>97</v>
       </c>
@@ -11879,7 +11883,7 @@
         <v>Punggol</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>84</v>
       </c>
@@ -11901,7 +11905,7 @@
         <v>Expo</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>56</v>
       </c>
@@ -11923,7 +11927,7 @@
         <v>Changi Airport</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>102</v>
       </c>
@@ -11945,7 +11949,7 @@
         <v>Sentosa</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>131</v>
       </c>
@@ -11956,7 +11960,7 @@
         <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F171" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(A171, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
@@ -11967,7 +11971,7 @@
         <v>Newton</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>85</v>
       </c>
@@ -11978,7 +11982,7 @@
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F172" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(A172, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
@@ -11989,15 +11993,26 @@
         <v>Tampines</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C173"/>
-      <c r="F173" t="e">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>128</v>
+      </c>
+      <c r="B173">
+        <v>113</v>
+      </c>
+      <c r="C173" s="2">
+        <v>2</v>
+      </c>
+      <c r="D173" t="s">
+        <v>184</v>
+      </c>
+      <c r="F173" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(A173, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G173" t="e">
+        <v>Choa Chu Kang</v>
+      </c>
+      <c r="G173" t="str">
         <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(B173, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>#N/A</v>
+        <v>Yew Tee</v>
       </c>
     </row>
   </sheetData>
@@ -12007,31 +12022,31 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6350115-3CCE-4A01-AEF1-ED551D546024}">
-  <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="21.5546875" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1" t="s">
         <v>365</v>
       </c>
-      <c r="B1" t="s">
-        <v>366</v>
-      </c>
       <c r="C1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1" t="s">
         <v>373</v>
       </c>
-      <c r="D1" t="s">
-        <v>374</v>
-      </c>
       <c r="E1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -12040,7 +12055,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>147</v>
       </c>
@@ -12048,7 +12063,7 @@
         <v>357</v>
       </c>
       <c r="C2">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -12069,12 +12084,12 @@
         <v>NS27</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -12098,7 +12113,7 @@
         <v>TE20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>177</v>
       </c>
@@ -12127,7 +12142,7 @@
         <v>CE2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>29</v>
       </c>
@@ -12156,7 +12171,7 @@
         <v>CC22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>28</v>
       </c>
@@ -12185,7 +12200,7 @@
         <v>EW21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25</v>
       </c>
@@ -12214,7 +12229,7 @@
         <v>CC19</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>24</v>
       </c>
@@ -12243,7 +12258,7 @@
         <v>DT9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>174</v>
       </c>
@@ -12272,7 +12287,7 @@
         <v>CC17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>173</v>
       </c>
@@ -12301,7 +12316,7 @@
         <v>TE9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>100</v>
       </c>
@@ -12330,7 +12345,7 @@
         <v>CC29</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>101</v>
       </c>
@@ -12359,7 +12374,7 @@
         <v>NE1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>58</v>
       </c>
@@ -12388,7 +12403,7 @@
         <v>DT10</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>57</v>
       </c>
@@ -12417,7 +12432,7 @@
         <v>TE11</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>108</v>
       </c>
@@ -12446,12 +12461,12 @@
         <v>EW16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -12475,7 +12490,7 @@
         <v>NE3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>107</v>
       </c>
@@ -12483,10 +12498,10 @@
         <v>356</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.43998999999999999</v>
       </c>
       <c r="D17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -12504,7 +12519,7 @@
         <v>TE17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>129</v>
       </c>
@@ -12526,14 +12541,14 @@
       </c>
       <c r="H18">
         <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A18, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>0.53085020054281096</v>
+        <v>0.53340053769933204</v>
       </c>
       <c r="I18" t="str">
         <f>INDEX(station_line!$D:$D, MATCH(A18, station_line!$A:$A, 0))</f>
         <v>NS17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>130</v>
       </c>
@@ -12555,14 +12570,14 @@
       </c>
       <c r="H19">
         <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A19, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>0.53085020054281096</v>
+        <v>0.53340053769933204</v>
       </c>
       <c r="I19" t="str">
         <f>INDEX(station_line!$D:$D, MATCH(A19, station_line!$A:$A, 0))</f>
         <v>CC15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>104</v>
       </c>
@@ -12591,7 +12606,7 @@
         <v>NE4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>103</v>
       </c>
@@ -12620,7 +12635,7 @@
         <v>DT19</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>139</v>
       </c>
@@ -12649,12 +12664,12 @@
         <v>NS24</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>141</v>
       </c>
       <c r="B23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -12678,7 +12693,7 @@
         <v>NE6</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>140</v>
       </c>
@@ -12707,7 +12722,7 @@
         <v>CC1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>143</v>
       </c>
@@ -12736,7 +12751,7 @@
         <v>NS9</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>142</v>
       </c>
@@ -12765,7 +12780,7 @@
         <v>TE2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>135</v>
       </c>
@@ -12787,14 +12802,14 @@
       </c>
       <c r="H27">
         <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A27, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>0.60480997808192805</v>
+        <v>0.60566009046743496</v>
       </c>
       <c r="I27" t="str">
         <f>INDEX(station_line!$D:$D, MATCH(A27, station_line!$A:$A, 0))</f>
         <v>NS25</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>136</v>
       </c>
@@ -12816,14 +12831,14 @@
       </c>
       <c r="H28">
         <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A28, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>0.60480997808192805</v>
+        <v>0.60566009046743496</v>
       </c>
       <c r="I28" t="str">
         <f>INDEX(station_line!$D:$D, MATCH(A28, station_line!$A:$A, 0))</f>
         <v>EW13</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>137</v>
       </c>
@@ -12852,7 +12867,7 @@
         <v>NS26</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>138</v>
       </c>
@@ -12881,7 +12896,7 @@
         <v>EW14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -12889,7 +12904,7 @@
         <v>357</v>
       </c>
       <c r="C31">
-        <v>0.71</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
@@ -12910,7 +12925,7 @@
         <v>DT16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -12939,7 +12954,7 @@
         <v>CE1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>20</v>
       </c>
@@ -12947,7 +12962,7 @@
         <v>357</v>
       </c>
       <c r="C33">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
@@ -12968,7 +12983,7 @@
         <v>DT15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>21</v>
       </c>
@@ -12997,7 +13012,7 @@
         <v>CC4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>99</v>
       </c>
@@ -13026,7 +13041,7 @@
         <v>NE12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>98</v>
       </c>
@@ -13055,7 +13070,7 @@
         <v>CC13</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>22</v>
       </c>
@@ -13084,7 +13099,7 @@
         <v>DT26</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>23</v>
       </c>
@@ -13113,7 +13128,7 @@
         <v>CC10</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>87</v>
       </c>
@@ -13142,7 +13157,7 @@
         <v>EW12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>88</v>
       </c>
@@ -13171,7 +13186,7 @@
         <v>DT14</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>106</v>
       </c>
@@ -13200,7 +13215,7 @@
         <v>NE7</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>105</v>
       </c>
@@ -13229,7 +13244,7 @@
         <v>DT12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>83</v>
       </c>
@@ -13258,7 +13273,7 @@
         <v>EW4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>84</v>
       </c>
@@ -13287,7 +13302,7 @@
         <v>CG</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>56</v>
       </c>
@@ -13316,7 +13331,7 @@
         <v>CG1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>55</v>
       </c>
@@ -13345,7 +13360,7 @@
         <v>DT35</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>171</v>
       </c>
@@ -13374,7 +13389,7 @@
         <v>TE31</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>172</v>
       </c>
@@ -13403,7 +13418,7 @@
         <v>DT37</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>26</v>
       </c>
@@ -13432,7 +13447,7 @@
         <v>EW8</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>27</v>
       </c>
@@ -13461,7 +13476,7 @@
         <v>CC9</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>144</v>
       </c>
@@ -13469,10 +13484,10 @@
         <v>357</v>
       </c>
       <c r="C51">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="D51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -13483,14 +13498,14 @@
       </c>
       <c r="H51">
         <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A51, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>0.44413873722108799</v>
+        <v>0.42543626473993201</v>
       </c>
       <c r="I51" t="str">
         <f>INDEX(station_line!$D:$D, MATCH(A51, station_line!$A:$A, 0))</f>
         <v>TE14</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>145</v>
       </c>
@@ -13512,11 +13527,69 @@
       </c>
       <c r="H52">
         <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A52, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
-        <v>0.44413873722108799</v>
+        <v>0.42543626473993201</v>
       </c>
       <c r="I52" t="str">
         <f>INDEX(station_line!$D:$D, MATCH(A52, station_line!$A:$A, 0))</f>
         <v>NS22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="str">
+        <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(A53, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
+        <v>Jurong East</v>
+      </c>
+      <c r="H53">
+        <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A53, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
+        <v>0.16360165000374699</v>
+      </c>
+      <c r="I53" t="str">
+        <f>INDEX(station_line!$D:$D, MATCH(A53, station_line!$A:$A, 0))</f>
+        <v>EW24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>133</v>
+      </c>
+      <c r="B54" t="s">
+        <v>357</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="str">
+        <f>INDEX(stations!$B:$B, MATCH(INDEX(station_line!$B:$B, MATCH(A54, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
+        <v>Jurong East</v>
+      </c>
+      <c r="H54">
+        <f>INDEX(stations!$C:$C, MATCH(INDEX(station_line!$B:$B, MATCH(A54, station_line!$A:$A, 0)), stations!$A:$A, 0))</f>
+        <v>0.16360165000374699</v>
+      </c>
+      <c r="I54" t="str">
+        <f>INDEX(station_line!$D:$D, MATCH(A54, station_line!$A:$A, 0))</f>
+        <v>NS1</v>
       </c>
     </row>
   </sheetData>
